--- a/file/мсб свод (общий) upload.xlsx
+++ b/file/мсб свод (общий) upload.xlsx
@@ -44,8 +44,8 @@
     <definedName name="_SHEET_ID1" localSheetId="3">1</definedName>
     <definedName name="_SHEET_ID2" localSheetId="4">1</definedName>
     <definedName name="_SHEET_ID20" localSheetId="0">1</definedName>
-    <definedName name="_SHEET_ID21" localSheetId="1">1</definedName>
-    <definedName name="_SHEET_ID22" localSheetId="2">1</definedName>
+    <definedName name="_SHEET_ID21" localSheetId="2">1</definedName>
+    <definedName name="_SHEET_ID22" localSheetId="1">1</definedName>
     <definedName name="_STATIC_REP_INTERNAL_KEY1">'Отчёт КПД ДО'!$5:$5</definedName>
     <definedName name="_STATIC_REP_SET_ROW1">'Отчёт КПД ДО'!$C:$D</definedName>
     <definedName name="_SUM_REP_INTERNAL_KEY1">'План общий '!$5:$5</definedName>
@@ -9003,6 +9003,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="4" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9113,9 +9116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10363,52 +10363,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="279" t="s">
+      <c r="B2" s="280" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="287" t="s">
+      <c r="C2" s="288" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="288"/>
-      <c r="E2" s="288"/>
-      <c r="F2" s="288"/>
-      <c r="G2" s="288"/>
-      <c r="H2" s="289"/>
-      <c r="I2" s="270" t="s">
+      <c r="D2" s="289"/>
+      <c r="E2" s="289"/>
+      <c r="F2" s="289"/>
+      <c r="G2" s="289"/>
+      <c r="H2" s="290"/>
+      <c r="I2" s="271" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="280"/>
-      <c r="C3" s="284" t="s">
+      <c r="B3" s="281"/>
+      <c r="C3" s="285" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="276" t="s">
+      <c r="D3" s="277" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="276" t="s">
+      <c r="E3" s="277" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="276" t="s">
+      <c r="F3" s="277" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="276" t="s">
+      <c r="G3" s="277" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="276" t="s">
+      <c r="H3" s="277" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="271"/>
+      <c r="I3" s="272"/>
     </row>
     <row r="4" spans="2:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="274"/>
-      <c r="C4" s="285"/>
-      <c r="D4" s="272"/>
-      <c r="E4" s="272"/>
-      <c r="F4" s="272"/>
-      <c r="G4" s="272"/>
-      <c r="H4" s="272"/>
-      <c r="I4" s="272"/>
+      <c r="B4" s="275"/>
+      <c r="C4" s="286"/>
+      <c r="D4" s="273"/>
+      <c r="E4" s="273"/>
+      <c r="F4" s="273"/>
+      <c r="G4" s="273"/>
+      <c r="H4" s="273"/>
+      <c r="I4" s="273"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="43"/>
@@ -10420,15 +10420,13 @@
       <c r="H5" s="43"/>
       <c r="I5" s="43"/>
     </row>
-    <row r="6" spans="2:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="45" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="45"/>
       <c r="D6" s="45"/>
-      <c r="E6" s="45">
-        <v>1</v>
-      </c>
+      <c r="E6" s="45"/>
       <c r="F6" s="45"/>
       <c r="G6" s="45"/>
       <c r="H6" s="45"/>
@@ -10436,15 +10434,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="47" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="47"/>
       <c r="D7" s="47"/>
-      <c r="E7" s="47">
-        <v>2</v>
-      </c>
+      <c r="E7" s="47"/>
       <c r="F7" s="47"/>
       <c r="G7" s="47"/>
       <c r="H7" s="47"/>
@@ -10452,15 +10448,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="47" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="47"/>
       <c r="D8" s="47"/>
-      <c r="E8" s="47">
-        <v>3</v>
-      </c>
+      <c r="E8" s="47"/>
       <c r="F8" s="47"/>
       <c r="G8" s="47"/>
       <c r="H8" s="47"/>
@@ -10468,15 +10462,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="45" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="45"/>
       <c r="D9" s="45"/>
-      <c r="E9" s="45">
-        <v>4</v>
-      </c>
+      <c r="E9" s="45"/>
       <c r="F9" s="45"/>
       <c r="G9" s="45"/>
       <c r="H9" s="45"/>
@@ -10484,15 +10476,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="47" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="47"/>
       <c r="D10" s="47"/>
-      <c r="E10" s="47">
-        <v>5</v>
-      </c>
+      <c r="E10" s="47"/>
       <c r="F10" s="47"/>
       <c r="G10" s="47"/>
       <c r="H10" s="47"/>
@@ -10500,15 +10490,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="47" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="47"/>
       <c r="D11" s="47"/>
-      <c r="E11" s="47">
-        <v>6</v>
-      </c>
+      <c r="E11" s="47"/>
       <c r="F11" s="47"/>
       <c r="G11" s="47"/>
       <c r="H11" s="47"/>
@@ -10516,15 +10504,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="49" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="49"/>
       <c r="D12" s="49"/>
-      <c r="E12" s="49">
-        <v>7</v>
-      </c>
+      <c r="E12" s="49"/>
       <c r="F12" s="49"/>
       <c r="G12" s="49"/>
       <c r="H12" s="49"/>
@@ -10532,15 +10518,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="49" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="49"/>
       <c r="D13" s="49"/>
-      <c r="E13" s="49">
-        <v>8</v>
-      </c>
+      <c r="E13" s="49"/>
       <c r="F13" s="49"/>
       <c r="G13" s="49"/>
       <c r="H13" s="49"/>
@@ -10548,13 +10532,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="50"/>
       <c r="C14" s="50"/>
       <c r="D14" s="50"/>
-      <c r="E14" s="50">
-        <v>9</v>
-      </c>
+      <c r="E14" s="50"/>
       <c r="F14" s="50"/>
       <c r="G14" s="50"/>
       <c r="H14" s="50"/>
@@ -10566,9 +10548,7 @@
       </c>
       <c r="C15" s="44"/>
       <c r="D15" s="44"/>
-      <c r="E15" s="44">
-        <v>10</v>
-      </c>
+      <c r="E15" s="44"/>
       <c r="F15" s="44"/>
       <c r="G15" s="44"/>
       <c r="H15" s="44"/>
@@ -10580,9 +10560,7 @@
       </c>
       <c r="C16" s="44"/>
       <c r="D16" s="44"/>
-      <c r="E16" s="44">
-        <v>11</v>
-      </c>
+      <c r="E16" s="44"/>
       <c r="F16" s="44"/>
       <c r="G16" s="44"/>
       <c r="H16" s="44"/>
@@ -10594,9 +10572,7 @@
       </c>
       <c r="C17" s="51"/>
       <c r="D17" s="51"/>
-      <c r="E17" s="51">
-        <v>12</v>
-      </c>
+      <c r="E17" s="51"/>
       <c r="F17" s="51"/>
       <c r="G17" s="51"/>
       <c r="H17" s="51"/>
@@ -10606,9 +10582,7 @@
       <c r="B18" s="53"/>
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
-      <c r="E18" s="53">
-        <v>13</v>
-      </c>
+      <c r="E18" s="53"/>
       <c r="F18" s="53"/>
       <c r="G18" s="53"/>
       <c r="H18" s="53"/>
@@ -10636,9 +10610,7 @@
       </c>
       <c r="C20" s="234"/>
       <c r="D20" s="234"/>
-      <c r="E20" s="235">
-        <v>14</v>
-      </c>
+      <c r="E20" s="235"/>
       <c r="F20" s="232"/>
       <c r="G20" s="231"/>
       <c r="H20" s="242"/>
@@ -10748,9 +10720,7 @@
       </c>
       <c r="C27" s="234"/>
       <c r="D27" s="234"/>
-      <c r="E27" s="235">
-        <v>15</v>
-      </c>
+      <c r="E27" s="235"/>
       <c r="F27" s="232"/>
       <c r="G27" s="231"/>
       <c r="H27" s="242"/>
@@ -10764,9 +10734,7 @@
       </c>
       <c r="C28" s="234"/>
       <c r="D28" s="234"/>
-      <c r="E28" s="235">
-        <v>16</v>
-      </c>
+      <c r="E28" s="235"/>
       <c r="F28" s="232"/>
       <c r="G28" s="231"/>
       <c r="H28" s="242"/>
@@ -10892,9 +10860,7 @@
       </c>
       <c r="C36" s="234"/>
       <c r="D36" s="234"/>
-      <c r="E36" s="235">
-        <v>17</v>
-      </c>
+      <c r="E36" s="235"/>
       <c r="F36" s="232"/>
       <c r="G36" s="231"/>
       <c r="H36" s="242"/>
@@ -10908,9 +10874,7 @@
       </c>
       <c r="C37" s="234"/>
       <c r="D37" s="234"/>
-      <c r="E37" s="235">
-        <v>18</v>
-      </c>
+      <c r="E37" s="235"/>
       <c r="F37" s="232"/>
       <c r="G37" s="231"/>
       <c r="H37" s="242"/>
@@ -10924,9 +10888,7 @@
       </c>
       <c r="C38" s="234"/>
       <c r="D38" s="234"/>
-      <c r="E38" s="235">
-        <v>19</v>
-      </c>
+      <c r="E38" s="235"/>
       <c r="F38" s="232"/>
       <c r="G38" s="231"/>
       <c r="H38" s="242"/>
@@ -10940,9 +10902,7 @@
       </c>
       <c r="C39" s="234"/>
       <c r="D39" s="234"/>
-      <c r="E39" s="235">
-        <v>20</v>
-      </c>
+      <c r="E39" s="235"/>
       <c r="F39" s="232"/>
       <c r="G39" s="231"/>
       <c r="H39" s="242"/>
@@ -10956,9 +10916,7 @@
       </c>
       <c r="C40" s="234"/>
       <c r="D40" s="234"/>
-      <c r="E40" s="235">
-        <v>21</v>
-      </c>
+      <c r="E40" s="235"/>
       <c r="F40" s="232"/>
       <c r="G40" s="231"/>
       <c r="H40" s="242"/>
@@ -11020,9 +10978,7 @@
       </c>
       <c r="C44" s="234"/>
       <c r="D44" s="234"/>
-      <c r="E44" s="235">
-        <v>22</v>
-      </c>
+      <c r="E44" s="235"/>
       <c r="F44" s="232"/>
       <c r="G44" s="231"/>
       <c r="H44" s="242"/>
@@ -11276,9 +11232,7 @@
       </c>
       <c r="C60" s="234"/>
       <c r="D60" s="234"/>
-      <c r="E60" s="235">
-        <v>23</v>
-      </c>
+      <c r="E60" s="235"/>
       <c r="F60" s="232"/>
       <c r="G60" s="231"/>
       <c r="H60" s="242"/>
@@ -11292,9 +11246,7 @@
       </c>
       <c r="C61" s="234"/>
       <c r="D61" s="234"/>
-      <c r="E61" s="235">
-        <v>24</v>
-      </c>
+      <c r="E61" s="235"/>
       <c r="F61" s="232"/>
       <c r="G61" s="231"/>
       <c r="H61" s="242"/>
@@ -11308,9 +11260,7 @@
       </c>
       <c r="C62" s="234"/>
       <c r="D62" s="234"/>
-      <c r="E62" s="235">
-        <v>25</v>
-      </c>
+      <c r="E62" s="235"/>
       <c r="F62" s="232"/>
       <c r="G62" s="231"/>
       <c r="H62" s="242"/>
@@ -11324,9 +11274,7 @@
       </c>
       <c r="C63" s="234"/>
       <c r="D63" s="234"/>
-      <c r="E63" s="235">
-        <v>26</v>
-      </c>
+      <c r="E63" s="235"/>
       <c r="F63" s="232"/>
       <c r="G63" s="231"/>
       <c r="H63" s="242"/>
@@ -11338,9 +11286,7 @@
       <c r="B64" s="81"/>
       <c r="C64" s="234"/>
       <c r="D64" s="234"/>
-      <c r="E64" s="235">
-        <v>27</v>
-      </c>
+      <c r="E64" s="235"/>
       <c r="F64" s="232"/>
       <c r="G64" s="231"/>
       <c r="H64" s="242"/>
@@ -11352,9 +11298,7 @@
       </c>
       <c r="C65" s="234"/>
       <c r="D65" s="234"/>
-      <c r="E65" s="235">
-        <v>28</v>
-      </c>
+      <c r="E65" s="235"/>
       <c r="F65" s="232"/>
       <c r="G65" s="231"/>
       <c r="H65" s="242"/>
@@ -11398,9 +11342,7 @@
       </c>
       <c r="C68" s="234"/>
       <c r="D68" s="234"/>
-      <c r="E68" s="235">
-        <v>29</v>
-      </c>
+      <c r="E68" s="235"/>
       <c r="F68" s="232"/>
       <c r="G68" s="231"/>
       <c r="H68" s="242"/>
@@ -11444,9 +11386,7 @@
       </c>
       <c r="C71" s="234"/>
       <c r="D71" s="234"/>
-      <c r="E71" s="235">
-        <v>30</v>
-      </c>
+      <c r="E71" s="235"/>
       <c r="F71" s="232"/>
       <c r="G71" s="231"/>
       <c r="H71" s="242"/>
@@ -11488,9 +11428,7 @@
       <c r="B74" s="81"/>
       <c r="C74" s="234"/>
       <c r="D74" s="234"/>
-      <c r="E74" s="235">
-        <v>31</v>
-      </c>
+      <c r="E74" s="235"/>
       <c r="F74" s="232"/>
       <c r="G74" s="231"/>
       <c r="H74" s="242"/>
@@ -11502,9 +11440,7 @@
       </c>
       <c r="C75" s="234"/>
       <c r="D75" s="234"/>
-      <c r="E75" s="235">
-        <v>32</v>
-      </c>
+      <c r="E75" s="235"/>
       <c r="F75" s="232"/>
       <c r="G75" s="231"/>
       <c r="H75" s="242"/>
@@ -11686,9 +11622,7 @@
       <c r="B87" s="69"/>
       <c r="C87" s="234"/>
       <c r="D87" s="234"/>
-      <c r="E87" s="235">
-        <v>33</v>
-      </c>
+      <c r="E87" s="235"/>
       <c r="F87" s="232"/>
       <c r="G87" s="231"/>
       <c r="H87" s="242"/>
@@ -12292,9 +12226,7 @@
       </c>
       <c r="C125" s="234"/>
       <c r="D125" s="234"/>
-      <c r="E125" s="235">
-        <v>34</v>
-      </c>
+      <c r="E125" s="235"/>
       <c r="F125" s="232"/>
       <c r="G125" s="231"/>
       <c r="H125" s="242"/>
@@ -12546,9 +12478,7 @@
       <c r="B141" s="78"/>
       <c r="C141" s="234"/>
       <c r="D141" s="234"/>
-      <c r="E141" s="235">
-        <v>35</v>
-      </c>
+      <c r="E141" s="235"/>
       <c r="F141" s="232"/>
       <c r="G141" s="231"/>
       <c r="H141" s="242"/>
@@ -13022,9 +12952,7 @@
       <c r="B171" s="76"/>
       <c r="C171" s="234"/>
       <c r="D171" s="234"/>
-      <c r="E171" s="235">
-        <v>36</v>
-      </c>
+      <c r="E171" s="235"/>
       <c r="F171" s="232"/>
       <c r="G171" s="231"/>
       <c r="H171" s="242"/>
@@ -13132,9 +13060,7 @@
       </c>
       <c r="C178" s="234"/>
       <c r="D178" s="234"/>
-      <c r="E178" s="235">
-        <v>37</v>
-      </c>
+      <c r="E178" s="235"/>
       <c r="F178" s="232"/>
       <c r="G178" s="231"/>
       <c r="H178" s="242"/>
@@ -13370,9 +13296,7 @@
       <c r="B193" s="83"/>
       <c r="C193" s="234"/>
       <c r="D193" s="234"/>
-      <c r="E193" s="235">
-        <v>38</v>
-      </c>
+      <c r="E193" s="235"/>
       <c r="F193" s="232"/>
       <c r="G193" s="231"/>
       <c r="H193" s="242"/>
@@ -13464,9 +13388,7 @@
       </c>
       <c r="C199" s="234"/>
       <c r="D199" s="234"/>
-      <c r="E199" s="235">
-        <v>39</v>
-      </c>
+      <c r="E199" s="235"/>
       <c r="F199" s="232"/>
       <c r="G199" s="231"/>
       <c r="H199" s="242"/>
@@ -13670,9 +13592,7 @@
       <c r="B212" s="102"/>
       <c r="C212" s="234"/>
       <c r="D212" s="234"/>
-      <c r="E212" s="235">
-        <v>40</v>
-      </c>
+      <c r="E212" s="235"/>
       <c r="F212" s="232"/>
       <c r="G212" s="231"/>
       <c r="H212" s="242"/>
@@ -13682,9 +13602,7 @@
       <c r="B213" s="75"/>
       <c r="C213" s="234"/>
       <c r="D213" s="234"/>
-      <c r="E213" s="235">
-        <v>41</v>
-      </c>
+      <c r="E213" s="235"/>
       <c r="F213" s="232"/>
       <c r="G213" s="231"/>
       <c r="H213" s="242"/>
@@ -13696,9 +13614,7 @@
       </c>
       <c r="C214" s="234"/>
       <c r="D214" s="234"/>
-      <c r="E214" s="235">
-        <v>42</v>
-      </c>
+      <c r="E214" s="235"/>
       <c r="F214" s="232"/>
       <c r="G214" s="231"/>
       <c r="H214" s="242"/>
@@ -13948,9 +13864,7 @@
       <c r="B230" s="81"/>
       <c r="C230" s="234"/>
       <c r="D230" s="234"/>
-      <c r="E230" s="235">
-        <v>43</v>
-      </c>
+      <c r="E230" s="235"/>
       <c r="F230" s="232"/>
       <c r="G230" s="231"/>
       <c r="H230" s="242"/>
@@ -13962,9 +13876,7 @@
       </c>
       <c r="C231" s="234"/>
       <c r="D231" s="234"/>
-      <c r="E231" s="235">
-        <v>44</v>
-      </c>
+      <c r="E231" s="235"/>
       <c r="F231" s="232"/>
       <c r="G231" s="231"/>
       <c r="H231" s="242"/>
@@ -14070,9 +13982,7 @@
       <c r="B238" s="88"/>
       <c r="C238" s="234"/>
       <c r="D238" s="234"/>
-      <c r="E238" s="235">
-        <v>45</v>
-      </c>
+      <c r="E238" s="235"/>
       <c r="F238" s="232"/>
       <c r="G238" s="231"/>
       <c r="H238" s="242"/>
@@ -14082,9 +13992,7 @@
       <c r="B239" s="202"/>
       <c r="C239" s="234"/>
       <c r="D239" s="234"/>
-      <c r="E239" s="235">
-        <v>46</v>
-      </c>
+      <c r="E239" s="235"/>
       <c r="F239" s="232"/>
       <c r="G239" s="231"/>
       <c r="H239" s="242"/>
@@ -14208,9 +14116,7 @@
       </c>
       <c r="C247" s="234"/>
       <c r="D247" s="234"/>
-      <c r="E247" s="235">
-        <v>47</v>
-      </c>
+      <c r="E247" s="235"/>
       <c r="F247" s="232"/>
       <c r="G247" s="231"/>
       <c r="H247" s="242"/>
@@ -14222,9 +14128,7 @@
       <c r="B248" s="106"/>
       <c r="C248" s="234"/>
       <c r="D248" s="234"/>
-      <c r="E248" s="235">
-        <v>48</v>
-      </c>
+      <c r="E248" s="235"/>
       <c r="F248" s="232"/>
       <c r="G248" s="231"/>
       <c r="H248" s="242"/>
@@ -14236,9 +14140,7 @@
       </c>
       <c r="C249" s="234"/>
       <c r="D249" s="234"/>
-      <c r="E249" s="235">
-        <v>49</v>
-      </c>
+      <c r="E249" s="235"/>
       <c r="F249" s="232"/>
       <c r="G249" s="231"/>
       <c r="H249" s="242"/>
@@ -14458,9 +14360,7 @@
       </c>
       <c r="C263" s="234"/>
       <c r="D263" s="234"/>
-      <c r="E263" s="235">
-        <v>50</v>
-      </c>
+      <c r="E263" s="235"/>
       <c r="F263" s="232"/>
       <c r="G263" s="231"/>
       <c r="H263" s="242"/>
@@ -14474,9 +14374,7 @@
       </c>
       <c r="C264" s="234"/>
       <c r="D264" s="234"/>
-      <c r="E264" s="235">
-        <v>51</v>
-      </c>
+      <c r="E264" s="235"/>
       <c r="F264" s="232"/>
       <c r="G264" s="231"/>
       <c r="H264" s="242"/>
@@ -14570,9 +14468,7 @@
       </c>
       <c r="C270" s="234"/>
       <c r="D270" s="234"/>
-      <c r="E270" s="235">
-        <v>52</v>
-      </c>
+      <c r="E270" s="235"/>
       <c r="F270" s="232"/>
       <c r="G270" s="231"/>
       <c r="H270" s="242"/>
@@ -14814,9 +14710,7 @@
       <c r="B286" s="123"/>
       <c r="C286" s="234"/>
       <c r="D286" s="234"/>
-      <c r="E286" s="235">
-        <v>53</v>
-      </c>
+      <c r="E286" s="235"/>
       <c r="F286" s="232"/>
       <c r="G286" s="231"/>
       <c r="H286" s="242"/>
@@ -14826,9 +14720,7 @@
       <c r="B287" s="93"/>
       <c r="C287" s="234"/>
       <c r="D287" s="234"/>
-      <c r="E287" s="235">
-        <v>54</v>
-      </c>
+      <c r="E287" s="235"/>
       <c r="F287" s="232"/>
       <c r="G287" s="231"/>
       <c r="H287" s="242"/>
@@ -14840,9 +14732,7 @@
       </c>
       <c r="C288" s="234"/>
       <c r="D288" s="234"/>
-      <c r="E288" s="235">
-        <v>55</v>
-      </c>
+      <c r="E288" s="235"/>
       <c r="F288" s="232"/>
       <c r="G288" s="231"/>
       <c r="H288" s="242"/>
@@ -14884,9 +14774,7 @@
       <c r="B291" s="123"/>
       <c r="C291" s="234"/>
       <c r="D291" s="234"/>
-      <c r="E291" s="235">
-        <v>56</v>
-      </c>
+      <c r="E291" s="235"/>
       <c r="F291" s="232"/>
       <c r="G291" s="231"/>
       <c r="H291" s="242"/>
@@ -14898,9 +14786,7 @@
       </c>
       <c r="C292" s="234"/>
       <c r="D292" s="234"/>
-      <c r="E292" s="235">
-        <v>57</v>
-      </c>
+      <c r="E292" s="235"/>
       <c r="F292" s="232"/>
       <c r="G292" s="231"/>
       <c r="H292" s="242"/>
@@ -14912,9 +14798,7 @@
       </c>
       <c r="C293" s="234"/>
       <c r="D293" s="234"/>
-      <c r="E293" s="235">
-        <v>58</v>
-      </c>
+      <c r="E293" s="235"/>
       <c r="F293" s="232"/>
       <c r="G293" s="231"/>
       <c r="H293" s="242"/>
@@ -14926,9 +14810,7 @@
       </c>
       <c r="C294" s="234"/>
       <c r="D294" s="234"/>
-      <c r="E294" s="235">
-        <v>59</v>
-      </c>
+      <c r="E294" s="235"/>
       <c r="F294" s="232"/>
       <c r="G294" s="231"/>
       <c r="H294" s="242"/>
@@ -14940,9 +14822,7 @@
       <c r="B295" s="89"/>
       <c r="C295" s="234"/>
       <c r="D295" s="234"/>
-      <c r="E295" s="235">
-        <v>60</v>
-      </c>
+      <c r="E295" s="235"/>
       <c r="F295" s="232"/>
       <c r="G295" s="231"/>
       <c r="H295" s="242"/>
@@ -14954,9 +14834,7 @@
       </c>
       <c r="C296" s="234"/>
       <c r="D296" s="234"/>
-      <c r="E296" s="235">
-        <v>61</v>
-      </c>
+      <c r="E296" s="235"/>
       <c r="F296" s="232"/>
       <c r="G296" s="231"/>
       <c r="H296" s="242"/>
@@ -14966,9 +14844,7 @@
       <c r="B297" s="202"/>
       <c r="C297" s="234"/>
       <c r="D297" s="234"/>
-      <c r="E297" s="235">
-        <v>62</v>
-      </c>
+      <c r="E297" s="235"/>
       <c r="F297" s="232"/>
       <c r="G297" s="231"/>
       <c r="H297" s="242"/>
@@ -15656,9 +15532,7 @@
       </c>
       <c r="C342" s="234"/>
       <c r="D342" s="234"/>
-      <c r="E342" s="235">
-        <v>63</v>
-      </c>
+      <c r="E342" s="235"/>
       <c r="F342" s="232"/>
       <c r="G342" s="231"/>
       <c r="H342" s="242"/>
@@ -15672,9 +15546,7 @@
       </c>
       <c r="C343" s="234"/>
       <c r="D343" s="234"/>
-      <c r="E343" s="235">
-        <v>64</v>
-      </c>
+      <c r="E343" s="235"/>
       <c r="F343" s="232"/>
       <c r="G343" s="231"/>
       <c r="H343" s="242"/>
@@ -15688,9 +15560,7 @@
       </c>
       <c r="C344" s="234"/>
       <c r="D344" s="234"/>
-      <c r="E344" s="235">
-        <v>65</v>
-      </c>
+      <c r="E344" s="235"/>
       <c r="F344" s="232"/>
       <c r="G344" s="231"/>
       <c r="H344" s="242"/>
@@ -15704,9 +15574,7 @@
       </c>
       <c r="C345" s="234"/>
       <c r="D345" s="234"/>
-      <c r="E345" s="235">
-        <v>66</v>
-      </c>
+      <c r="E345" s="235"/>
       <c r="F345" s="232"/>
       <c r="G345" s="231"/>
       <c r="H345" s="242"/>
@@ -15904,9 +15772,7 @@
       </c>
       <c r="C358" s="234"/>
       <c r="D358" s="234"/>
-      <c r="E358" s="235">
-        <v>67</v>
-      </c>
+      <c r="E358" s="235"/>
       <c r="F358" s="232"/>
       <c r="G358" s="231"/>
       <c r="H358" s="242"/>
@@ -15918,9 +15784,7 @@
       <c r="B359" s="106"/>
       <c r="C359" s="234"/>
       <c r="D359" s="234"/>
-      <c r="E359" s="235">
-        <v>68</v>
-      </c>
+      <c r="E359" s="235"/>
       <c r="F359" s="232"/>
       <c r="G359" s="231"/>
       <c r="H359" s="242"/>
@@ -16076,9 +15940,7 @@
       <c r="B369" s="120"/>
       <c r="C369" s="234"/>
       <c r="D369" s="234"/>
-      <c r="E369" s="235">
-        <v>69</v>
-      </c>
+      <c r="E369" s="235"/>
       <c r="F369" s="232"/>
       <c r="G369" s="231"/>
       <c r="H369" s="242"/>
@@ -16090,9 +15952,7 @@
       </c>
       <c r="C370" s="234"/>
       <c r="D370" s="234"/>
-      <c r="E370" s="235">
-        <v>70</v>
-      </c>
+      <c r="E370" s="235"/>
       <c r="F370" s="232"/>
       <c r="G370" s="231"/>
       <c r="H370" s="242"/>
@@ -16136,9 +15996,7 @@
       </c>
       <c r="C373" s="234"/>
       <c r="D373" s="234"/>
-      <c r="E373" s="235">
-        <v>71</v>
-      </c>
+      <c r="E373" s="235"/>
       <c r="F373" s="232"/>
       <c r="G373" s="231"/>
       <c r="H373" s="242"/>
@@ -16182,9 +16040,7 @@
       </c>
       <c r="C376" s="234"/>
       <c r="D376" s="234"/>
-      <c r="E376" s="235">
-        <v>72</v>
-      </c>
+      <c r="E376" s="235"/>
       <c r="F376" s="232"/>
       <c r="G376" s="231"/>
       <c r="H376" s="242"/>
@@ -16226,9 +16082,7 @@
       <c r="B379" s="75"/>
       <c r="C379" s="234"/>
       <c r="D379" s="234"/>
-      <c r="E379" s="235">
-        <v>73</v>
-      </c>
+      <c r="E379" s="235"/>
       <c r="F379" s="232"/>
       <c r="G379" s="231"/>
       <c r="H379" s="242"/>
@@ -16240,9 +16094,7 @@
       </c>
       <c r="C380" s="234"/>
       <c r="D380" s="234"/>
-      <c r="E380" s="235">
-        <v>74</v>
-      </c>
+      <c r="E380" s="235"/>
       <c r="F380" s="232"/>
       <c r="G380" s="231"/>
       <c r="H380" s="242"/>
@@ -16256,9 +16108,7 @@
       </c>
       <c r="C381" s="234"/>
       <c r="D381" s="234"/>
-      <c r="E381" s="235">
-        <v>75</v>
-      </c>
+      <c r="E381" s="235"/>
       <c r="F381" s="232"/>
       <c r="G381" s="231"/>
       <c r="H381" s="242"/>
@@ -16272,9 +16122,7 @@
       </c>
       <c r="C382" s="234"/>
       <c r="D382" s="234"/>
-      <c r="E382" s="235">
-        <v>76</v>
-      </c>
+      <c r="E382" s="235"/>
       <c r="F382" s="232"/>
       <c r="G382" s="231"/>
       <c r="H382" s="242"/>
@@ -16286,9 +16134,7 @@
       <c r="B383" s="103"/>
       <c r="C383" s="234"/>
       <c r="D383" s="234"/>
-      <c r="E383" s="235">
-        <v>77</v>
-      </c>
+      <c r="E383" s="235"/>
       <c r="F383" s="232"/>
       <c r="G383" s="231"/>
       <c r="H383" s="242"/>
@@ -16302,9 +16148,7 @@
       </c>
       <c r="C384" s="234"/>
       <c r="D384" s="234"/>
-      <c r="E384" s="235">
-        <v>78</v>
-      </c>
+      <c r="E384" s="235"/>
       <c r="F384" s="232"/>
       <c r="G384" s="231"/>
       <c r="H384" s="242"/>
@@ -16318,9 +16162,7 @@
       </c>
       <c r="C385" s="234"/>
       <c r="D385" s="234"/>
-      <c r="E385" s="235">
-        <v>79</v>
-      </c>
+      <c r="E385" s="235"/>
       <c r="F385" s="232"/>
       <c r="G385" s="231"/>
       <c r="H385" s="242"/>
@@ -16334,9 +16176,7 @@
       </c>
       <c r="C386" s="234"/>
       <c r="D386" s="234"/>
-      <c r="E386" s="235">
-        <v>80</v>
-      </c>
+      <c r="E386" s="235"/>
       <c r="F386" s="232"/>
       <c r="G386" s="231"/>
       <c r="H386" s="242"/>
@@ -16348,9 +16188,7 @@
       <c r="B387" s="103"/>
       <c r="C387" s="234"/>
       <c r="D387" s="234"/>
-      <c r="E387" s="235">
-        <v>81</v>
-      </c>
+      <c r="E387" s="235"/>
       <c r="F387" s="232"/>
       <c r="G387" s="231"/>
       <c r="H387" s="242"/>
@@ -16364,9 +16202,7 @@
       </c>
       <c r="C388" s="234"/>
       <c r="D388" s="234"/>
-      <c r="E388" s="235">
-        <v>82</v>
-      </c>
+      <c r="E388" s="235"/>
       <c r="F388" s="232"/>
       <c r="G388" s="231"/>
       <c r="H388" s="242"/>
@@ -16378,9 +16214,7 @@
       <c r="B389" s="123"/>
       <c r="C389" s="234"/>
       <c r="D389" s="234"/>
-      <c r="E389" s="235">
-        <v>83</v>
-      </c>
+      <c r="E389" s="235"/>
       <c r="F389" s="232"/>
       <c r="G389" s="231"/>
       <c r="H389" s="242"/>
@@ -16392,9 +16226,7 @@
       </c>
       <c r="C390" s="234"/>
       <c r="D390" s="234"/>
-      <c r="E390" s="235">
-        <v>84</v>
-      </c>
+      <c r="E390" s="235"/>
       <c r="F390" s="232"/>
       <c r="G390" s="231"/>
       <c r="H390" s="242"/>
@@ -16482,9 +16314,7 @@
       </c>
       <c r="C396" s="234"/>
       <c r="D396" s="234"/>
-      <c r="E396" s="235">
-        <v>85</v>
-      </c>
+      <c r="E396" s="235"/>
       <c r="F396" s="232"/>
       <c r="G396" s="231"/>
       <c r="H396" s="242"/>
@@ -16640,9 +16470,7 @@
       </c>
       <c r="C406" s="234"/>
       <c r="D406" s="234"/>
-      <c r="E406" s="235">
-        <v>86</v>
-      </c>
+      <c r="E406" s="235"/>
       <c r="F406" s="232"/>
       <c r="G406" s="231"/>
       <c r="H406" s="242"/>
@@ -16688,9 +16516,7 @@
       </c>
       <c r="C409" s="234"/>
       <c r="D409" s="234"/>
-      <c r="E409" s="235">
-        <v>87</v>
-      </c>
+      <c r="E409" s="235"/>
       <c r="F409" s="232"/>
       <c r="G409" s="231"/>
       <c r="H409" s="242"/>
@@ -16734,9 +16560,7 @@
       </c>
       <c r="C412" s="234"/>
       <c r="D412" s="234"/>
-      <c r="E412" s="235">
-        <v>88</v>
-      </c>
+      <c r="E412" s="235"/>
       <c r="F412" s="232"/>
       <c r="G412" s="231"/>
       <c r="H412" s="242"/>
@@ -16828,9 +16652,7 @@
       <c r="B418" s="76"/>
       <c r="C418" s="234"/>
       <c r="D418" s="234"/>
-      <c r="E418" s="235">
-        <v>89</v>
-      </c>
+      <c r="E418" s="235"/>
       <c r="F418" s="232"/>
       <c r="G418" s="231"/>
       <c r="H418" s="242"/>
@@ -16842,9 +16664,7 @@
       </c>
       <c r="C419" s="234"/>
       <c r="D419" s="234"/>
-      <c r="E419" s="235">
-        <v>90</v>
-      </c>
+      <c r="E419" s="235"/>
       <c r="F419" s="232"/>
       <c r="G419" s="231"/>
       <c r="H419" s="242"/>
@@ -16856,9 +16676,7 @@
       </c>
       <c r="C420" s="234"/>
       <c r="D420" s="234"/>
-      <c r="E420" s="235">
-        <v>91</v>
-      </c>
+      <c r="E420" s="235"/>
       <c r="F420" s="232"/>
       <c r="G420" s="231"/>
       <c r="H420" s="242"/>
@@ -16950,9 +16768,7 @@
       </c>
       <c r="C426" s="234"/>
       <c r="D426" s="234"/>
-      <c r="E426" s="235">
-        <v>92</v>
-      </c>
+      <c r="E426" s="235"/>
       <c r="F426" s="232"/>
       <c r="G426" s="231"/>
       <c r="H426" s="242"/>
@@ -17122,9 +16938,7 @@
       <c r="B437" s="88"/>
       <c r="C437" s="234"/>
       <c r="D437" s="234"/>
-      <c r="E437" s="235">
-        <v>93</v>
-      </c>
+      <c r="E437" s="235"/>
       <c r="F437" s="232"/>
       <c r="G437" s="231"/>
       <c r="H437" s="242"/>
@@ -17440,9 +17254,7 @@
       </c>
       <c r="C457" s="234"/>
       <c r="D457" s="234"/>
-      <c r="E457" s="235">
-        <v>94</v>
-      </c>
+      <c r="E457" s="235"/>
       <c r="F457" s="232"/>
       <c r="G457" s="231"/>
       <c r="H457" s="242"/>
@@ -17488,9 +17300,7 @@
       </c>
       <c r="C460" s="234"/>
       <c r="D460" s="234"/>
-      <c r="E460" s="235">
-        <v>95</v>
-      </c>
+      <c r="E460" s="235"/>
       <c r="F460" s="232"/>
       <c r="G460" s="231"/>
       <c r="H460" s="242"/>
@@ -18014,9 +17824,7 @@
       <c r="B493" s="106"/>
       <c r="C493" s="234"/>
       <c r="D493" s="234"/>
-      <c r="E493" s="235">
-        <v>96</v>
-      </c>
+      <c r="E493" s="235"/>
       <c r="F493" s="232"/>
       <c r="G493" s="231"/>
       <c r="H493" s="242"/>
@@ -18328,9 +18136,7 @@
       <c r="B513" s="95"/>
       <c r="C513" s="234"/>
       <c r="D513" s="234"/>
-      <c r="E513" s="235">
-        <v>97</v>
-      </c>
+      <c r="E513" s="235"/>
       <c r="F513" s="232"/>
       <c r="G513" s="231"/>
       <c r="H513" s="242"/>
@@ -18342,9 +18148,7 @@
       </c>
       <c r="C514" s="234"/>
       <c r="D514" s="234"/>
-      <c r="E514" s="235">
-        <v>98</v>
-      </c>
+      <c r="E514" s="235"/>
       <c r="F514" s="232"/>
       <c r="G514" s="231"/>
       <c r="H514" s="242"/>
@@ -19140,9 +18944,7 @@
       </c>
       <c r="C564" s="234"/>
       <c r="D564" s="234"/>
-      <c r="E564" s="235">
-        <v>99</v>
-      </c>
+      <c r="E564" s="235"/>
       <c r="F564" s="232"/>
       <c r="G564" s="231"/>
       <c r="H564" s="242"/>
@@ -19156,9 +18958,7 @@
       </c>
       <c r="C565" s="234"/>
       <c r="D565" s="234"/>
-      <c r="E565" s="235">
-        <v>100</v>
-      </c>
+      <c r="E565" s="235"/>
       <c r="F565" s="232"/>
       <c r="G565" s="231"/>
       <c r="H565" s="242"/>
@@ -19650,9 +19450,7 @@
       <c r="B596" s="106"/>
       <c r="C596" s="234"/>
       <c r="D596" s="234"/>
-      <c r="E596" s="235">
-        <v>101</v>
-      </c>
+      <c r="E596" s="235"/>
       <c r="F596" s="232"/>
       <c r="G596" s="231"/>
       <c r="H596" s="242"/>
@@ -19664,9 +19462,7 @@
       </c>
       <c r="C597" s="234"/>
       <c r="D597" s="234"/>
-      <c r="E597" s="235">
-        <v>102</v>
-      </c>
+      <c r="E597" s="235"/>
       <c r="F597" s="232"/>
       <c r="G597" s="231"/>
       <c r="H597" s="242"/>
@@ -20904,9 +20700,7 @@
       <c r="B675" s="89"/>
       <c r="C675" s="234"/>
       <c r="D675" s="234"/>
-      <c r="E675" s="235">
-        <v>103</v>
-      </c>
+      <c r="E675" s="235"/>
       <c r="F675" s="232"/>
       <c r="G675" s="231"/>
       <c r="H675" s="242"/>
@@ -20982,9 +20776,7 @@
       </c>
       <c r="C680" s="234"/>
       <c r="D680" s="234"/>
-      <c r="E680" s="235">
-        <v>104</v>
-      </c>
+      <c r="E680" s="235"/>
       <c r="F680" s="232"/>
       <c r="G680" s="231"/>
       <c r="H680" s="242"/>
@@ -21202,9 +20994,7 @@
       <c r="B694" s="120"/>
       <c r="C694" s="234"/>
       <c r="D694" s="234"/>
-      <c r="E694" s="235">
-        <v>105</v>
-      </c>
+      <c r="E694" s="235"/>
       <c r="F694" s="232"/>
       <c r="G694" s="231"/>
       <c r="H694" s="242"/>
@@ -21216,9 +21006,7 @@
       </c>
       <c r="C695" s="234"/>
       <c r="D695" s="234"/>
-      <c r="E695" s="235">
-        <v>106</v>
-      </c>
+      <c r="E695" s="235"/>
       <c r="F695" s="232"/>
       <c r="G695" s="231"/>
       <c r="H695" s="242"/>
@@ -21372,9 +21160,7 @@
       <c r="B705" s="88"/>
       <c r="C705" s="234"/>
       <c r="D705" s="234"/>
-      <c r="E705" s="235">
-        <v>107</v>
-      </c>
+      <c r="E705" s="235"/>
       <c r="F705" s="232"/>
       <c r="G705" s="231"/>
       <c r="H705" s="242"/>
@@ -21624,9 +21410,7 @@
       <c r="B721" s="89"/>
       <c r="C721" s="234"/>
       <c r="D721" s="234"/>
-      <c r="E721" s="235">
-        <v>108</v>
-      </c>
+      <c r="E721" s="235"/>
       <c r="F721" s="232"/>
       <c r="G721" s="231"/>
       <c r="H721" s="242"/>
@@ -21748,9 +21532,7 @@
       <c r="B729" s="88"/>
       <c r="C729" s="234"/>
       <c r="D729" s="234"/>
-      <c r="E729" s="235">
-        <v>109</v>
-      </c>
+      <c r="E729" s="235"/>
       <c r="F729" s="232"/>
       <c r="G729" s="231"/>
       <c r="H729" s="242"/>
@@ -22000,9 +21782,7 @@
       <c r="B745" s="89"/>
       <c r="C745" s="234"/>
       <c r="D745" s="234"/>
-      <c r="E745" s="235">
-        <v>110</v>
-      </c>
+      <c r="E745" s="235"/>
       <c r="F745" s="232"/>
       <c r="G745" s="231"/>
       <c r="H745" s="242"/>
@@ -22156,9 +21936,7 @@
       <c r="B755" s="89"/>
       <c r="C755" s="234"/>
       <c r="D755" s="234"/>
-      <c r="E755" s="235">
-        <v>111</v>
-      </c>
+      <c r="E755" s="235"/>
       <c r="F755" s="232"/>
       <c r="G755" s="231"/>
       <c r="H755" s="242"/>
@@ -22312,9 +22090,7 @@
       <c r="B765" s="202"/>
       <c r="C765" s="234"/>
       <c r="D765" s="234"/>
-      <c r="E765" s="235">
-        <v>112</v>
-      </c>
+      <c r="E765" s="235"/>
       <c r="F765" s="232"/>
       <c r="G765" s="231"/>
       <c r="H765" s="242"/>
@@ -22454,9 +22230,7 @@
       </c>
       <c r="C774" s="234"/>
       <c r="D774" s="234"/>
-      <c r="E774" s="235">
-        <v>113</v>
-      </c>
+      <c r="E774" s="235"/>
       <c r="F774" s="232"/>
       <c r="G774" s="231"/>
       <c r="H774" s="242"/>
@@ -22546,9 +22320,7 @@
       <c r="B780" s="106"/>
       <c r="C780" s="234"/>
       <c r="D780" s="234"/>
-      <c r="E780" s="235">
-        <v>114</v>
-      </c>
+      <c r="E780" s="235"/>
       <c r="F780" s="232"/>
       <c r="G780" s="231"/>
       <c r="H780" s="242"/>
@@ -22960,9 +22732,7 @@
       <c r="B807" s="106"/>
       <c r="C807" s="234"/>
       <c r="D807" s="234"/>
-      <c r="E807" s="235">
-        <v>115</v>
-      </c>
+      <c r="E807" s="235"/>
       <c r="F807" s="232"/>
       <c r="G807" s="231"/>
       <c r="H807" s="242"/>
@@ -22974,9 +22744,7 @@
       </c>
       <c r="C808" s="234"/>
       <c r="D808" s="234"/>
-      <c r="E808" s="235">
-        <v>116</v>
-      </c>
+      <c r="E808" s="235"/>
       <c r="F808" s="232"/>
       <c r="G808" s="231"/>
       <c r="H808" s="242"/>
@@ -23098,9 +22866,7 @@
       <c r="B816" s="120"/>
       <c r="C816" s="234"/>
       <c r="D816" s="234"/>
-      <c r="E816" s="235">
-        <v>117</v>
-      </c>
+      <c r="E816" s="235"/>
       <c r="F816" s="232"/>
       <c r="G816" s="231"/>
       <c r="H816" s="242"/>
@@ -23112,9 +22878,7 @@
       </c>
       <c r="C817" s="234"/>
       <c r="D817" s="234"/>
-      <c r="E817" s="235">
-        <v>118</v>
-      </c>
+      <c r="E817" s="235"/>
       <c r="F817" s="232"/>
       <c r="G817" s="231"/>
       <c r="H817" s="242"/>
@@ -23158,9 +22922,7 @@
       </c>
       <c r="C820" s="234"/>
       <c r="D820" s="234"/>
-      <c r="E820" s="235">
-        <v>119</v>
-      </c>
+      <c r="E820" s="235"/>
       <c r="F820" s="232"/>
       <c r="G820" s="231"/>
       <c r="H820" s="242"/>
@@ -23250,9 +23012,7 @@
       <c r="B826" s="106"/>
       <c r="C826" s="234"/>
       <c r="D826" s="234"/>
-      <c r="E826" s="235">
-        <v>120</v>
-      </c>
+      <c r="E826" s="235"/>
       <c r="F826" s="232"/>
       <c r="G826" s="231"/>
       <c r="H826" s="242"/>
@@ -23264,9 +23024,7 @@
       </c>
       <c r="C827" s="234"/>
       <c r="D827" s="234"/>
-      <c r="E827" s="235">
-        <v>121</v>
-      </c>
+      <c r="E827" s="235"/>
       <c r="F827" s="232"/>
       <c r="G827" s="231"/>
       <c r="H827" s="242"/>
@@ -23336,9 +23094,7 @@
       <c r="B832" s="88"/>
       <c r="C832" s="234"/>
       <c r="D832" s="234"/>
-      <c r="E832" s="235">
-        <v>122</v>
-      </c>
+      <c r="E832" s="235"/>
       <c r="F832" s="232"/>
       <c r="G832" s="231"/>
       <c r="H832" s="242"/>
@@ -23350,9 +23106,7 @@
       </c>
       <c r="C833" s="234"/>
       <c r="D833" s="234"/>
-      <c r="E833" s="235">
-        <v>123</v>
-      </c>
+      <c r="E833" s="235"/>
       <c r="F833" s="232"/>
       <c r="G833" s="231"/>
       <c r="H833" s="242"/>
@@ -23452,9 +23206,7 @@
       <c r="B840" s="88"/>
       <c r="C840" s="234"/>
       <c r="D840" s="234"/>
-      <c r="E840" s="235">
-        <v>124</v>
-      </c>
+      <c r="E840" s="235"/>
       <c r="F840" s="232"/>
       <c r="G840" s="231"/>
       <c r="H840" s="242"/>
@@ -24064,9 +23816,7 @@
       <c r="B881" s="120"/>
       <c r="C881" s="234"/>
       <c r="D881" s="234"/>
-      <c r="E881" s="235">
-        <v>125</v>
-      </c>
+      <c r="E881" s="235"/>
       <c r="F881" s="232"/>
       <c r="G881" s="231"/>
       <c r="H881" s="242"/>
@@ -24078,9 +23828,7 @@
       </c>
       <c r="C882" s="234"/>
       <c r="D882" s="234"/>
-      <c r="E882" s="235">
-        <v>126</v>
-      </c>
+      <c r="E882" s="235"/>
       <c r="F882" s="232"/>
       <c r="G882" s="231"/>
       <c r="H882" s="242"/>
@@ -24152,9 +23900,7 @@
       </c>
       <c r="C887" s="234"/>
       <c r="D887" s="234"/>
-      <c r="E887" s="235">
-        <v>127</v>
-      </c>
+      <c r="E887" s="235"/>
       <c r="F887" s="232"/>
       <c r="G887" s="231"/>
       <c r="H887" s="242"/>
@@ -24254,9 +24000,7 @@
       <c r="B894" s="88"/>
       <c r="C894" s="234"/>
       <c r="D894" s="234"/>
-      <c r="E894" s="235">
-        <v>128</v>
-      </c>
+      <c r="E894" s="235"/>
       <c r="F894" s="232"/>
       <c r="G894" s="231"/>
       <c r="H894" s="242"/>
@@ -24628,9 +24372,7 @@
       </c>
       <c r="C919" s="234"/>
       <c r="D919" s="234"/>
-      <c r="E919" s="235">
-        <v>129</v>
-      </c>
+      <c r="E919" s="235"/>
       <c r="F919" s="232"/>
       <c r="G919" s="231"/>
       <c r="H919" s="242"/>
@@ -24642,9 +24384,7 @@
       <c r="B920" s="88"/>
       <c r="C920" s="234"/>
       <c r="D920" s="234"/>
-      <c r="E920" s="235">
-        <v>130</v>
-      </c>
+      <c r="E920" s="235"/>
       <c r="F920" s="232"/>
       <c r="G920" s="231"/>
       <c r="H920" s="242"/>
@@ -24658,9 +24398,7 @@
       </c>
       <c r="C921" s="234"/>
       <c r="D921" s="234"/>
-      <c r="E921" s="235">
-        <v>131</v>
-      </c>
+      <c r="E921" s="235"/>
       <c r="F921" s="232"/>
       <c r="G921" s="231"/>
       <c r="H921" s="242"/>
@@ -24672,9 +24410,7 @@
       <c r="B922" s="109"/>
       <c r="C922" s="234"/>
       <c r="D922" s="234"/>
-      <c r="E922" s="235">
-        <v>132</v>
-      </c>
+      <c r="E922" s="235"/>
       <c r="F922" s="232"/>
       <c r="G922" s="231"/>
       <c r="H922" s="242"/>
@@ -24686,9 +24422,7 @@
       <c r="B923" s="120"/>
       <c r="C923" s="234"/>
       <c r="D923" s="234"/>
-      <c r="E923" s="235">
-        <v>133</v>
-      </c>
+      <c r="E923" s="235"/>
       <c r="F923" s="232"/>
       <c r="G923" s="231"/>
       <c r="H923" s="242"/>
@@ -24892,9 +24626,7 @@
       </c>
       <c r="C936" s="234"/>
       <c r="D936" s="234"/>
-      <c r="E936" s="235">
-        <v>134</v>
-      </c>
+      <c r="E936" s="235"/>
       <c r="F936" s="232"/>
       <c r="G936" s="231"/>
       <c r="H936" s="242"/>
@@ -24906,9 +24638,7 @@
       <c r="B937" s="202"/>
       <c r="C937" s="234"/>
       <c r="D937" s="234"/>
-      <c r="E937" s="235">
-        <v>135</v>
-      </c>
+      <c r="E937" s="235"/>
       <c r="F937" s="232"/>
       <c r="G937" s="231"/>
       <c r="H937" s="242"/>
@@ -24920,9 +24650,7 @@
       </c>
       <c r="C938" s="234"/>
       <c r="D938" s="234"/>
-      <c r="E938" s="235">
-        <v>136</v>
-      </c>
+      <c r="E938" s="235"/>
       <c r="F938" s="232"/>
       <c r="G938" s="231"/>
       <c r="H938" s="242"/>
@@ -24932,9 +24660,7 @@
       <c r="B939" s="123"/>
       <c r="C939" s="234"/>
       <c r="D939" s="234"/>
-      <c r="E939" s="235">
-        <v>137</v>
-      </c>
+      <c r="E939" s="235"/>
       <c r="F939" s="232"/>
       <c r="G939" s="231"/>
       <c r="H939" s="242"/>
@@ -24948,9 +24674,7 @@
       </c>
       <c r="C940" s="234"/>
       <c r="D940" s="234"/>
-      <c r="E940" s="235">
-        <v>138</v>
-      </c>
+      <c r="E940" s="235"/>
       <c r="F940" s="232"/>
       <c r="G940" s="231"/>
       <c r="H940" s="242"/>
@@ -24964,9 +24688,7 @@
       </c>
       <c r="C941" s="234"/>
       <c r="D941" s="234"/>
-      <c r="E941" s="235">
-        <v>139</v>
-      </c>
+      <c r="E941" s="235"/>
       <c r="F941" s="232"/>
       <c r="G941" s="231"/>
       <c r="H941" s="242"/>
@@ -24980,9 +24702,7 @@
       </c>
       <c r="C942" s="234"/>
       <c r="D942" s="234"/>
-      <c r="E942" s="235">
-        <v>140</v>
-      </c>
+      <c r="E942" s="235"/>
       <c r="F942" s="232"/>
       <c r="G942" s="231"/>
       <c r="H942" s="242"/>
@@ -24996,9 +24716,7 @@
       </c>
       <c r="C943" s="234"/>
       <c r="D943" s="234"/>
-      <c r="E943" s="235">
-        <v>141</v>
-      </c>
+      <c r="E943" s="235"/>
       <c r="F943" s="232"/>
       <c r="G943" s="231"/>
       <c r="H943" s="242"/>
@@ -25012,9 +24730,7 @@
       </c>
       <c r="C944" s="234"/>
       <c r="D944" s="234"/>
-      <c r="E944" s="235">
-        <v>142</v>
-      </c>
+      <c r="E944" s="235"/>
       <c r="F944" s="232"/>
       <c r="G944" s="231"/>
       <c r="H944" s="242"/>
@@ -25028,9 +24744,7 @@
       </c>
       <c r="C945" s="234"/>
       <c r="D945" s="234"/>
-      <c r="E945" s="235">
-        <v>143</v>
-      </c>
+      <c r="E945" s="235"/>
       <c r="F945" s="232"/>
       <c r="G945" s="231"/>
       <c r="H945" s="242"/>
@@ -25042,9 +24756,7 @@
       <c r="B946" s="123"/>
       <c r="C946" s="234"/>
       <c r="D946" s="234"/>
-      <c r="E946" s="235">
-        <v>144</v>
-      </c>
+      <c r="E946" s="235"/>
       <c r="F946" s="232"/>
       <c r="G946" s="231"/>
       <c r="H946" s="242"/>
@@ -25054,9 +24766,7 @@
       <c r="B947" s="123"/>
       <c r="C947" s="234"/>
       <c r="D947" s="234"/>
-      <c r="E947" s="235">
-        <v>145</v>
-      </c>
+      <c r="E947" s="235"/>
       <c r="F947" s="232"/>
       <c r="G947" s="231"/>
       <c r="H947" s="242"/>
@@ -25068,9 +24778,7 @@
       </c>
       <c r="C948" s="234"/>
       <c r="D948" s="234"/>
-      <c r="E948" s="235">
-        <v>146</v>
-      </c>
+      <c r="E948" s="235"/>
       <c r="F948" s="232"/>
       <c r="G948" s="231"/>
       <c r="H948" s="242"/>
@@ -25080,9 +24788,7 @@
       <c r="B949" s="123"/>
       <c r="C949" s="234"/>
       <c r="D949" s="234"/>
-      <c r="E949" s="235">
-        <v>147</v>
-      </c>
+      <c r="E949" s="235"/>
       <c r="F949" s="232"/>
       <c r="G949" s="231"/>
       <c r="H949" s="242"/>
@@ -25094,9 +24800,7 @@
       </c>
       <c r="C950" s="234"/>
       <c r="D950" s="234"/>
-      <c r="E950" s="235">
-        <v>148</v>
-      </c>
+      <c r="E950" s="235"/>
       <c r="F950" s="232"/>
       <c r="G950" s="231"/>
       <c r="H950" s="242"/>
@@ -25124,9 +24828,7 @@
       </c>
       <c r="C952" s="234"/>
       <c r="D952" s="234"/>
-      <c r="E952" s="235">
-        <v>149</v>
-      </c>
+      <c r="E952" s="235"/>
       <c r="F952" s="232"/>
       <c r="G952" s="231"/>
       <c r="H952" s="242"/>
@@ -25136,9 +24838,7 @@
       <c r="B953" s="125"/>
       <c r="C953" s="234"/>
       <c r="D953" s="234"/>
-      <c r="E953" s="235">
-        <v>150</v>
-      </c>
+      <c r="E953" s="235"/>
       <c r="F953" s="232"/>
       <c r="G953" s="231"/>
       <c r="H953" s="242"/>
@@ -25148,9 +24848,7 @@
       <c r="B954" s="126"/>
       <c r="C954" s="234"/>
       <c r="D954" s="234"/>
-      <c r="E954" s="235">
-        <v>151</v>
-      </c>
+      <c r="E954" s="235"/>
       <c r="F954" s="232"/>
       <c r="G954" s="231"/>
       <c r="H954" s="242"/>
@@ -25162,9 +24860,7 @@
       </c>
       <c r="C955" s="234"/>
       <c r="D955" s="234"/>
-      <c r="E955" s="235">
-        <v>152</v>
-      </c>
+      <c r="E955" s="235"/>
       <c r="F955" s="232"/>
       <c r="G955" s="231"/>
       <c r="H955" s="242"/>
@@ -25176,9 +24872,7 @@
       </c>
       <c r="C956" s="234"/>
       <c r="D956" s="234"/>
-      <c r="E956" s="235">
-        <v>153</v>
-      </c>
+      <c r="E956" s="235"/>
       <c r="F956" s="232"/>
       <c r="G956" s="231"/>
       <c r="H956" s="242"/>
@@ -25192,9 +24886,7 @@
       </c>
       <c r="C957" s="234"/>
       <c r="D957" s="234"/>
-      <c r="E957" s="235">
-        <v>154</v>
-      </c>
+      <c r="E957" s="235"/>
       <c r="F957" s="232"/>
       <c r="G957" s="231"/>
       <c r="H957" s="242"/>
@@ -25204,9 +24896,7 @@
       <c r="B958" s="128"/>
       <c r="C958" s="234"/>
       <c r="D958" s="234"/>
-      <c r="E958" s="235">
-        <v>155</v>
-      </c>
+      <c r="E958" s="235"/>
       <c r="F958" s="232"/>
       <c r="G958" s="231"/>
       <c r="H958" s="242"/>
@@ -25216,9 +24906,7 @@
       <c r="B959" s="125"/>
       <c r="C959" s="234"/>
       <c r="D959" s="234"/>
-      <c r="E959" s="235">
-        <v>156</v>
-      </c>
+      <c r="E959" s="235"/>
       <c r="F959" s="232"/>
       <c r="G959" s="231"/>
       <c r="H959" s="242"/>
@@ -25228,9 +24916,7 @@
       <c r="B960" s="125"/>
       <c r="C960" s="234"/>
       <c r="D960" s="234"/>
-      <c r="E960" s="235">
-        <v>157</v>
-      </c>
+      <c r="E960" s="235"/>
       <c r="F960" s="232"/>
       <c r="G960" s="231"/>
       <c r="H960" s="242"/>
@@ -25242,9 +24928,7 @@
       </c>
       <c r="C961" s="234"/>
       <c r="D961" s="234"/>
-      <c r="E961" s="235">
-        <v>158</v>
-      </c>
+      <c r="E961" s="235"/>
       <c r="F961" s="232"/>
       <c r="G961" s="231"/>
       <c r="H961" s="242"/>
@@ -25256,9 +24940,7 @@
       </c>
       <c r="C962" s="234"/>
       <c r="D962" s="234"/>
-      <c r="E962" s="235">
-        <v>159</v>
-      </c>
+      <c r="E962" s="235"/>
       <c r="F962" s="232"/>
       <c r="G962" s="231"/>
       <c r="H962" s="242"/>
@@ -25268,9 +24950,7 @@
       <c r="B963" s="131"/>
       <c r="C963" s="234"/>
       <c r="D963" s="234"/>
-      <c r="E963" s="235">
-        <v>160</v>
-      </c>
+      <c r="E963" s="235"/>
       <c r="F963" s="232"/>
       <c r="G963" s="231"/>
       <c r="H963" s="242"/>
@@ -25282,9 +24962,7 @@
       </c>
       <c r="C964" s="234"/>
       <c r="D964" s="234"/>
-      <c r="E964" s="235">
-        <v>161</v>
-      </c>
+      <c r="E964" s="235"/>
       <c r="F964" s="232"/>
       <c r="G964" s="231"/>
       <c r="H964" s="242"/>
@@ -25294,9 +24972,7 @@
       <c r="B965" s="88"/>
       <c r="C965" s="234"/>
       <c r="D965" s="234"/>
-      <c r="E965" s="235">
-        <v>162</v>
-      </c>
+      <c r="E965" s="235"/>
       <c r="F965" s="232"/>
       <c r="G965" s="231"/>
       <c r="H965" s="242"/>
@@ -25308,9 +24984,7 @@
       </c>
       <c r="C966" s="234"/>
       <c r="D966" s="234"/>
-      <c r="E966" s="235">
-        <v>163</v>
-      </c>
+      <c r="E966" s="235"/>
       <c r="F966" s="232"/>
       <c r="G966" s="231"/>
       <c r="H966" s="242"/>
@@ -25320,9 +24994,7 @@
       <c r="B967" s="135"/>
       <c r="C967" s="234"/>
       <c r="D967" s="234"/>
-      <c r="E967" s="235">
-        <v>164</v>
-      </c>
+      <c r="E967" s="235"/>
       <c r="F967" s="232"/>
       <c r="G967" s="231"/>
       <c r="H967" s="242"/>
@@ -25334,9 +25006,7 @@
       </c>
       <c r="C968" s="234"/>
       <c r="D968" s="234"/>
-      <c r="E968" s="235">
-        <v>165</v>
-      </c>
+      <c r="E968" s="235"/>
       <c r="F968" s="232"/>
       <c r="G968" s="231"/>
       <c r="H968" s="242"/>
@@ -25350,9 +25020,7 @@
       </c>
       <c r="C969" s="234"/>
       <c r="D969" s="234"/>
-      <c r="E969" s="235">
-        <v>166</v>
-      </c>
+      <c r="E969" s="235"/>
       <c r="F969" s="232"/>
       <c r="G969" s="231"/>
       <c r="H969" s="242"/>
@@ -25364,9 +25032,7 @@
       <c r="B970" s="133"/>
       <c r="C970" s="234"/>
       <c r="D970" s="234"/>
-      <c r="E970" s="235">
-        <v>167</v>
-      </c>
+      <c r="E970" s="235"/>
       <c r="F970" s="232"/>
       <c r="G970" s="231"/>
       <c r="H970" s="242"/>
@@ -25378,9 +25044,7 @@
       </c>
       <c r="C971" s="234"/>
       <c r="D971" s="234"/>
-      <c r="E971" s="235">
-        <v>168</v>
-      </c>
+      <c r="E971" s="235"/>
       <c r="F971" s="232"/>
       <c r="G971" s="231"/>
       <c r="H971" s="242"/>
@@ -25392,9 +25056,7 @@
       </c>
       <c r="C972" s="234"/>
       <c r="D972" s="234"/>
-      <c r="E972" s="235">
-        <v>169</v>
-      </c>
+      <c r="E972" s="235"/>
       <c r="F972" s="232"/>
       <c r="G972" s="231"/>
       <c r="H972" s="242"/>
@@ -25406,9 +25068,7 @@
       <c r="B973" s="133"/>
       <c r="C973" s="234"/>
       <c r="D973" s="234"/>
-      <c r="E973" s="235">
-        <v>170</v>
-      </c>
+      <c r="E973" s="235"/>
       <c r="F973" s="232"/>
       <c r="G973" s="231"/>
       <c r="H973" s="242"/>
@@ -25422,9 +25082,7 @@
       </c>
       <c r="C974" s="234"/>
       <c r="D974" s="234"/>
-      <c r="E974" s="235">
-        <v>171</v>
-      </c>
+      <c r="E974" s="235"/>
       <c r="F974" s="232"/>
       <c r="G974" s="231"/>
       <c r="H974" s="242"/>
@@ -25436,9 +25094,7 @@
       <c r="B975" s="136"/>
       <c r="C975" s="234"/>
       <c r="D975" s="234"/>
-      <c r="E975" s="235">
-        <v>172</v>
-      </c>
+      <c r="E975" s="235"/>
       <c r="F975" s="232"/>
       <c r="G975" s="231"/>
       <c r="H975" s="242"/>
@@ -25482,9 +25138,7 @@
       <c r="B978" s="120"/>
       <c r="C978" s="234"/>
       <c r="D978" s="234"/>
-      <c r="E978" s="235">
-        <v>173</v>
-      </c>
+      <c r="E978" s="235"/>
       <c r="F978" s="232"/>
       <c r="G978" s="231"/>
       <c r="H978" s="242"/>
@@ -25494,9 +25148,7 @@
       <c r="B979" s="135"/>
       <c r="C979" s="234"/>
       <c r="D979" s="234"/>
-      <c r="E979" s="235">
-        <v>174</v>
-      </c>
+      <c r="E979" s="235"/>
       <c r="F979" s="232"/>
       <c r="G979" s="231"/>
       <c r="H979" s="242"/>
@@ -25508,9 +25160,7 @@
       </c>
       <c r="C980" s="234"/>
       <c r="D980" s="234"/>
-      <c r="E980" s="235">
-        <v>175</v>
-      </c>
+      <c r="E980" s="235"/>
       <c r="F980" s="232"/>
       <c r="G980" s="231"/>
       <c r="H980" s="242"/>
@@ -25522,9 +25172,7 @@
       </c>
       <c r="C981" s="234"/>
       <c r="D981" s="234"/>
-      <c r="E981" s="235">
-        <v>176</v>
-      </c>
+      <c r="E981" s="235"/>
       <c r="F981" s="232"/>
       <c r="G981" s="231"/>
       <c r="H981" s="242"/>
@@ -25536,9 +25184,7 @@
       <c r="B982" s="135"/>
       <c r="C982" s="234"/>
       <c r="D982" s="234"/>
-      <c r="E982" s="235">
-        <v>177</v>
-      </c>
+      <c r="E982" s="235"/>
       <c r="F982" s="232"/>
       <c r="G982" s="231"/>
       <c r="H982" s="242"/>
@@ -25550,9 +25196,7 @@
       </c>
       <c r="C983" s="234"/>
       <c r="D983" s="234"/>
-      <c r="E983" s="235">
-        <v>178</v>
-      </c>
+      <c r="E983" s="235"/>
       <c r="F983" s="232"/>
       <c r="G983" s="231"/>
       <c r="H983" s="242"/>
@@ -25564,9 +25208,7 @@
       <c r="B984" s="139"/>
       <c r="C984" s="234"/>
       <c r="D984" s="234"/>
-      <c r="E984" s="235">
-        <v>179</v>
-      </c>
+      <c r="E984" s="235"/>
       <c r="F984" s="232"/>
       <c r="G984" s="231"/>
       <c r="H984" s="242"/>
@@ -25578,9 +25220,7 @@
       </c>
       <c r="C985" s="234"/>
       <c r="D985" s="234"/>
-      <c r="E985" s="235">
-        <v>180</v>
-      </c>
+      <c r="E985" s="235"/>
       <c r="F985" s="232"/>
       <c r="G985" s="231"/>
       <c r="H985" s="242"/>
@@ -25592,9 +25232,7 @@
       <c r="B986" s="135"/>
       <c r="C986" s="234"/>
       <c r="D986" s="234"/>
-      <c r="E986" s="235">
-        <v>181</v>
-      </c>
+      <c r="E986" s="235"/>
       <c r="F986" s="232"/>
       <c r="G986" s="231"/>
       <c r="H986" s="242"/>
@@ -25606,9 +25244,7 @@
       </c>
       <c r="C987" s="234"/>
       <c r="D987" s="234"/>
-      <c r="E987" s="235">
-        <v>182</v>
-      </c>
+      <c r="E987" s="235"/>
       <c r="F987" s="232"/>
       <c r="G987" s="231"/>
       <c r="H987" s="242"/>
@@ -25620,9 +25256,7 @@
       <c r="B988" s="135"/>
       <c r="C988" s="234"/>
       <c r="D988" s="234"/>
-      <c r="E988" s="235">
-        <v>183</v>
-      </c>
+      <c r="E988" s="235"/>
       <c r="F988" s="232"/>
       <c r="G988" s="231"/>
       <c r="H988" s="242"/>
@@ -25634,9 +25268,7 @@
       </c>
       <c r="C989" s="234"/>
       <c r="D989" s="234"/>
-      <c r="E989" s="235">
-        <v>184</v>
-      </c>
+      <c r="E989" s="235"/>
       <c r="F989" s="232"/>
       <c r="G989" s="231"/>
       <c r="H989" s="242"/>
@@ -25648,9 +25280,7 @@
       </c>
       <c r="C990" s="234"/>
       <c r="D990" s="234"/>
-      <c r="E990" s="235">
-        <v>185</v>
-      </c>
+      <c r="E990" s="235"/>
       <c r="F990" s="232"/>
       <c r="G990" s="231"/>
       <c r="H990" s="242"/>
@@ -25662,9 +25292,7 @@
       <c r="B991" s="133"/>
       <c r="C991" s="234"/>
       <c r="D991" s="234"/>
-      <c r="E991" s="235">
-        <v>186</v>
-      </c>
+      <c r="E991" s="235"/>
       <c r="F991" s="232"/>
       <c r="G991" s="231"/>
       <c r="H991" s="242"/>
@@ -25676,9 +25304,7 @@
       <c r="B992" s="136"/>
       <c r="C992" s="234"/>
       <c r="D992" s="234"/>
-      <c r="E992" s="235">
-        <v>187</v>
-      </c>
+      <c r="E992" s="235"/>
       <c r="F992" s="232"/>
       <c r="G992" s="231"/>
       <c r="H992" s="242"/>
@@ -25752,9 +25378,7 @@
       <c r="B997" s="135"/>
       <c r="C997" s="234"/>
       <c r="D997" s="234"/>
-      <c r="E997" s="235">
-        <v>188</v>
-      </c>
+      <c r="E997" s="235"/>
       <c r="F997" s="232"/>
       <c r="G997" s="231"/>
       <c r="H997" s="242"/>
@@ -25764,9 +25388,7 @@
       <c r="B998" s="135"/>
       <c r="C998" s="234"/>
       <c r="D998" s="234"/>
-      <c r="E998" s="235">
-        <v>189</v>
-      </c>
+      <c r="E998" s="235"/>
       <c r="F998" s="232"/>
       <c r="G998" s="231"/>
       <c r="H998" s="242"/>
@@ -25776,9 +25398,7 @@
       <c r="B999" s="135"/>
       <c r="C999" s="234"/>
       <c r="D999" s="234"/>
-      <c r="E999" s="235">
-        <v>190</v>
-      </c>
+      <c r="E999" s="235"/>
       <c r="F999" s="232"/>
       <c r="G999" s="231"/>
       <c r="H999" s="242"/>
@@ -25788,9 +25408,7 @@
       <c r="B1000" s="135"/>
       <c r="C1000" s="234"/>
       <c r="D1000" s="234"/>
-      <c r="E1000" s="235">
-        <v>191</v>
-      </c>
+      <c r="E1000" s="235"/>
       <c r="F1000" s="232"/>
       <c r="G1000" s="231"/>
       <c r="H1000" s="242"/>
@@ -25802,9 +25420,7 @@
       </c>
       <c r="C1001" s="234"/>
       <c r="D1001" s="234"/>
-      <c r="E1001" s="235">
-        <v>192</v>
-      </c>
+      <c r="E1001" s="235"/>
       <c r="F1001" s="232"/>
       <c r="G1001" s="231"/>
       <c r="H1001" s="242"/>
@@ -25814,9 +25430,7 @@
       <c r="B1002" s="143"/>
       <c r="C1002" s="234"/>
       <c r="D1002" s="234"/>
-      <c r="E1002" s="235">
-        <v>193</v>
-      </c>
+      <c r="E1002" s="235"/>
       <c r="F1002" s="232"/>
       <c r="G1002" s="231"/>
       <c r="H1002" s="242"/>
@@ -25855,7 +25469,7 @@
       </c>
     </row>
     <row r="1005" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1005" s="282" t="s">
+      <c r="B1005" s="283" t="s">
         <v>847</v>
       </c>
       <c r="C1005" s="234"/>
@@ -25871,7 +25485,7 @@
       </c>
     </row>
     <row r="1006" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1006" s="274"/>
+      <c r="B1006" s="275"/>
       <c r="C1006" s="234"/>
       <c r="D1006" s="234"/>
       <c r="E1006" s="235"/>
@@ -25949,7 +25563,7 @@
       </c>
     </row>
     <row r="1011" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1011" s="286" t="s">
+      <c r="B1011" s="287" t="s">
         <v>858</v>
       </c>
       <c r="C1011" s="234"/>
@@ -25965,7 +25579,7 @@
       </c>
     </row>
     <row r="1012" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1012" s="274"/>
+      <c r="B1012" s="275"/>
       <c r="C1012" s="234"/>
       <c r="D1012" s="234"/>
       <c r="E1012" s="235"/>
@@ -25979,7 +25593,7 @@
       </c>
     </row>
     <row r="1013" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1013" s="278" t="s">
+      <c r="B1013" s="279" t="s">
         <v>861</v>
       </c>
       <c r="C1013" s="234"/>
@@ -25995,7 +25609,7 @@
       </c>
     </row>
     <row r="1014" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1014" s="274"/>
+      <c r="B1014" s="275"/>
       <c r="C1014" s="234"/>
       <c r="D1014" s="234"/>
       <c r="E1014" s="235"/>
@@ -26009,7 +25623,7 @@
       </c>
     </row>
     <row r="1015" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1015" s="282" t="s">
+      <c r="B1015" s="283" t="s">
         <v>847</v>
       </c>
       <c r="C1015" s="234"/>
@@ -26025,7 +25639,7 @@
       </c>
     </row>
     <row r="1016" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1016" s="274"/>
+      <c r="B1016" s="275"/>
       <c r="C1016" s="234"/>
       <c r="D1016" s="234"/>
       <c r="E1016" s="235"/>
@@ -26039,7 +25653,7 @@
       </c>
     </row>
     <row r="1017" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1017" s="278" t="s">
+      <c r="B1017" s="279" t="s">
         <v>866</v>
       </c>
       <c r="C1017" s="234"/>
@@ -26055,7 +25669,7 @@
       </c>
     </row>
     <row r="1018" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1018" s="274"/>
+      <c r="B1018" s="275"/>
       <c r="C1018" s="234"/>
       <c r="D1018" s="234"/>
       <c r="E1018" s="235"/>
@@ -26069,7 +25683,7 @@
       </c>
     </row>
     <row r="1019" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1019" s="282" t="s">
+      <c r="B1019" s="283" t="s">
         <v>847</v>
       </c>
       <c r="C1019" s="234"/>
@@ -26085,7 +25699,7 @@
       </c>
     </row>
     <row r="1020" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1020" s="274"/>
+      <c r="B1020" s="275"/>
       <c r="C1020" s="234"/>
       <c r="D1020" s="234"/>
       <c r="E1020" s="235"/>
@@ -26131,7 +25745,7 @@
       </c>
     </row>
     <row r="1023" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1023" s="273" t="s">
+      <c r="B1023" s="274" t="s">
         <v>875</v>
       </c>
       <c r="C1023" s="234"/>
@@ -26147,7 +25761,7 @@
       </c>
     </row>
     <row r="1024" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1024" s="274"/>
+      <c r="B1024" s="275"/>
       <c r="C1024" s="234"/>
       <c r="D1024" s="234"/>
       <c r="E1024" s="235"/>
@@ -26337,7 +25951,7 @@
       </c>
     </row>
     <row r="1036" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1036" s="278" t="s">
+      <c r="B1036" s="279" t="s">
         <v>896</v>
       </c>
       <c r="C1036" s="234"/>
@@ -26353,7 +25967,7 @@
       </c>
     </row>
     <row r="1037" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1037" s="274"/>
+      <c r="B1037" s="275"/>
       <c r="C1037" s="234"/>
       <c r="D1037" s="234"/>
       <c r="E1037" s="235"/>
@@ -26367,7 +25981,7 @@
       </c>
     </row>
     <row r="1038" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1038" s="273" t="s">
+      <c r="B1038" s="274" t="s">
         <v>899</v>
       </c>
       <c r="C1038" s="234"/>
@@ -26383,7 +25997,7 @@
       </c>
     </row>
     <row r="1039" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1039" s="274"/>
+      <c r="B1039" s="275"/>
       <c r="C1039" s="234"/>
       <c r="D1039" s="234"/>
       <c r="E1039" s="235"/>
@@ -26397,7 +26011,7 @@
       </c>
     </row>
     <row r="1040" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1040" s="273" t="s">
+      <c r="B1040" s="274" t="s">
         <v>902</v>
       </c>
       <c r="C1040" s="234"/>
@@ -26413,7 +26027,7 @@
       </c>
     </row>
     <row r="1041" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1041" s="274"/>
+      <c r="B1041" s="275"/>
       <c r="C1041" s="234"/>
       <c r="D1041" s="234"/>
       <c r="E1041" s="235"/>
@@ -26427,7 +26041,7 @@
       </c>
     </row>
     <row r="1042" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1042" s="282" t="s">
+      <c r="B1042" s="283" t="s">
         <v>905</v>
       </c>
       <c r="C1042" s="234"/>
@@ -26443,7 +26057,7 @@
       </c>
     </row>
     <row r="1043" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1043" s="274"/>
+      <c r="B1043" s="275"/>
       <c r="C1043" s="234"/>
       <c r="D1043" s="234"/>
       <c r="E1043" s="235"/>
@@ -26457,7 +26071,7 @@
       </c>
     </row>
     <row r="1044" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1044" s="282" t="s">
+      <c r="B1044" s="283" t="s">
         <v>888</v>
       </c>
       <c r="C1044" s="234"/>
@@ -26473,7 +26087,7 @@
       </c>
     </row>
     <row r="1045" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1045" s="274"/>
+      <c r="B1045" s="275"/>
       <c r="C1045" s="234"/>
       <c r="D1045" s="234"/>
       <c r="E1045" s="235"/>
@@ -26487,7 +26101,7 @@
       </c>
     </row>
     <row r="1046" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1046" s="278" t="s">
+      <c r="B1046" s="279" t="s">
         <v>910</v>
       </c>
       <c r="C1046" s="234"/>
@@ -26503,7 +26117,7 @@
       </c>
     </row>
     <row r="1047" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1047" s="274"/>
+      <c r="B1047" s="275"/>
       <c r="C1047" s="234"/>
       <c r="D1047" s="234"/>
       <c r="E1047" s="235"/>
@@ -26517,7 +26131,7 @@
       </c>
     </row>
     <row r="1048" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1048" s="273" t="s">
+      <c r="B1048" s="274" t="s">
         <v>899</v>
       </c>
       <c r="C1048" s="234"/>
@@ -26533,7 +26147,7 @@
       </c>
     </row>
     <row r="1049" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1049" s="274"/>
+      <c r="B1049" s="275"/>
       <c r="C1049" s="234"/>
       <c r="D1049" s="234"/>
       <c r="E1049" s="235"/>
@@ -26547,7 +26161,7 @@
       </c>
     </row>
     <row r="1050" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1050" s="273" t="s">
+      <c r="B1050" s="274" t="s">
         <v>902</v>
       </c>
       <c r="C1050" s="234"/>
@@ -26563,7 +26177,7 @@
       </c>
     </row>
     <row r="1051" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1051" s="274"/>
+      <c r="B1051" s="275"/>
       <c r="C1051" s="234"/>
       <c r="D1051" s="234"/>
       <c r="E1051" s="235"/>
@@ -26577,7 +26191,7 @@
       </c>
     </row>
     <row r="1052" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1052" s="282" t="s">
+      <c r="B1052" s="283" t="s">
         <v>905</v>
       </c>
       <c r="C1052" s="234"/>
@@ -26593,7 +26207,7 @@
       </c>
     </row>
     <row r="1053" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1053" s="274"/>
+      <c r="B1053" s="275"/>
       <c r="C1053" s="234"/>
       <c r="D1053" s="234"/>
       <c r="E1053" s="235"/>
@@ -26607,7 +26221,7 @@
       </c>
     </row>
     <row r="1054" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1054" s="282" t="s">
+      <c r="B1054" s="283" t="s">
         <v>888</v>
       </c>
       <c r="C1054" s="234"/>
@@ -26623,7 +26237,7 @@
       </c>
     </row>
     <row r="1055" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1055" s="274"/>
+      <c r="B1055" s="275"/>
       <c r="C1055" s="234"/>
       <c r="D1055" s="234"/>
       <c r="E1055" s="235"/>
@@ -26733,7 +26347,7 @@
       </c>
     </row>
     <row r="1062" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1062" s="278" t="s">
+      <c r="B1062" s="279" t="s">
         <v>931</v>
       </c>
       <c r="C1062" s="234"/>
@@ -26749,7 +26363,7 @@
       </c>
     </row>
     <row r="1063" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1063" s="274"/>
+      <c r="B1063" s="275"/>
       <c r="C1063" s="234"/>
       <c r="D1063" s="234"/>
       <c r="E1063" s="235"/>
@@ -26763,7 +26377,7 @@
       </c>
     </row>
     <row r="1064" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1064" s="290" t="s">
+      <c r="B1064" s="291" t="s">
         <v>934</v>
       </c>
       <c r="C1064" s="234"/>
@@ -26779,7 +26393,7 @@
       </c>
     </row>
     <row r="1065" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1065" s="274"/>
+      <c r="B1065" s="275"/>
       <c r="C1065" s="234"/>
       <c r="D1065" s="234"/>
       <c r="E1065" s="235"/>
@@ -26793,7 +26407,7 @@
       </c>
     </row>
     <row r="1066" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1066" s="283" t="s">
+      <c r="B1066" s="284" t="s">
         <v>899</v>
       </c>
       <c r="C1066" s="234"/>
@@ -26809,7 +26423,7 @@
       </c>
     </row>
     <row r="1067" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1067" s="274"/>
+      <c r="B1067" s="275"/>
       <c r="C1067" s="234"/>
       <c r="D1067" s="234"/>
       <c r="E1067" s="235"/>
@@ -26823,7 +26437,7 @@
       </c>
     </row>
     <row r="1068" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1068" s="283" t="s">
+      <c r="B1068" s="284" t="s">
         <v>902</v>
       </c>
       <c r="C1068" s="234"/>
@@ -26839,7 +26453,7 @@
       </c>
     </row>
     <row r="1069" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1069" s="274"/>
+      <c r="B1069" s="275"/>
       <c r="C1069" s="234"/>
       <c r="D1069" s="234"/>
       <c r="E1069" s="235"/>
@@ -26853,7 +26467,7 @@
       </c>
     </row>
     <row r="1070" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1070" s="277" t="s">
+      <c r="B1070" s="278" t="s">
         <v>905</v>
       </c>
       <c r="C1070" s="234"/>
@@ -26869,7 +26483,7 @@
       </c>
     </row>
     <row r="1071" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1071" s="274"/>
+      <c r="B1071" s="275"/>
       <c r="C1071" s="234"/>
       <c r="D1071" s="234"/>
       <c r="E1071" s="235"/>
@@ -26883,7 +26497,7 @@
       </c>
     </row>
     <row r="1072" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1072" s="290" t="s">
+      <c r="B1072" s="291" t="s">
         <v>943</v>
       </c>
       <c r="C1072" s="234"/>
@@ -26899,7 +26513,7 @@
       </c>
     </row>
     <row r="1073" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1073" s="274"/>
+      <c r="B1073" s="275"/>
       <c r="C1073" s="234"/>
       <c r="D1073" s="234"/>
       <c r="E1073" s="235"/>
@@ -26913,7 +26527,7 @@
       </c>
     </row>
     <row r="1074" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1074" s="291" t="s">
+      <c r="B1074" s="292" t="s">
         <v>888</v>
       </c>
       <c r="C1074" s="234"/>
@@ -26929,7 +26543,7 @@
       </c>
     </row>
     <row r="1075" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1075" s="274"/>
+      <c r="B1075" s="275"/>
       <c r="C1075" s="234"/>
       <c r="D1075" s="234"/>
       <c r="E1075" s="235"/>
@@ -26943,7 +26557,7 @@
       </c>
     </row>
     <row r="1076" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1076" s="281" t="s">
+      <c r="B1076" s="282" t="s">
         <v>948</v>
       </c>
       <c r="C1076" s="234"/>
@@ -26959,7 +26573,7 @@
       </c>
     </row>
     <row r="1077" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1077" s="274"/>
+      <c r="B1077" s="275"/>
       <c r="C1077" s="234"/>
       <c r="D1077" s="234"/>
       <c r="E1077" s="235"/>
@@ -26973,7 +26587,7 @@
       </c>
     </row>
     <row r="1078" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1078" s="290" t="s">
+      <c r="B1078" s="291" t="s">
         <v>934</v>
       </c>
       <c r="C1078" s="234"/>
@@ -26989,7 +26603,7 @@
       </c>
     </row>
     <row r="1079" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1079" s="274"/>
+      <c r="B1079" s="275"/>
       <c r="C1079" s="234"/>
       <c r="D1079" s="234"/>
       <c r="E1079" s="235"/>
@@ -27003,7 +26617,7 @@
       </c>
     </row>
     <row r="1080" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1080" s="273" t="s">
+      <c r="B1080" s="274" t="s">
         <v>902</v>
       </c>
       <c r="C1080" s="234"/>
@@ -27019,7 +26633,7 @@
       </c>
     </row>
     <row r="1081" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1081" s="274"/>
+      <c r="B1081" s="275"/>
       <c r="C1081" s="234"/>
       <c r="D1081" s="234"/>
       <c r="E1081" s="235"/>
@@ -27033,7 +26647,7 @@
       </c>
     </row>
     <row r="1082" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1082" s="293" t="s">
+      <c r="B1082" s="294" t="s">
         <v>905</v>
       </c>
       <c r="C1082" s="234"/>
@@ -27049,7 +26663,7 @@
       </c>
     </row>
     <row r="1083" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1083" s="274"/>
+      <c r="B1083" s="275"/>
       <c r="C1083" s="234"/>
       <c r="D1083" s="234"/>
       <c r="E1083" s="235"/>
@@ -27063,7 +26677,7 @@
       </c>
     </row>
     <row r="1084" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1084" s="290" t="s">
+      <c r="B1084" s="291" t="s">
         <v>943</v>
       </c>
       <c r="C1084" s="234"/>
@@ -27079,7 +26693,7 @@
       </c>
     </row>
     <row r="1085" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1085" s="274"/>
+      <c r="B1085" s="275"/>
       <c r="C1085" s="234"/>
       <c r="D1085" s="234"/>
       <c r="E1085" s="235"/>
@@ -27093,7 +26707,7 @@
       </c>
     </row>
     <row r="1086" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1086" s="293" t="s">
+      <c r="B1086" s="294" t="s">
         <v>888</v>
       </c>
       <c r="C1086" s="234"/>
@@ -27109,7 +26723,7 @@
       </c>
     </row>
     <row r="1087" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1087" s="274"/>
+      <c r="B1087" s="275"/>
       <c r="C1087" s="234"/>
       <c r="D1087" s="234"/>
       <c r="E1087" s="235"/>
@@ -27126,9 +26740,7 @@
       <c r="B1088" s="151"/>
       <c r="C1088" s="234"/>
       <c r="D1088" s="234"/>
-      <c r="E1088" s="235">
-        <v>194</v>
-      </c>
+      <c r="E1088" s="235"/>
       <c r="F1088" s="232"/>
       <c r="G1088" s="231"/>
       <c r="H1088" s="242"/>
@@ -27140,9 +26752,7 @@
       </c>
       <c r="C1089" s="234"/>
       <c r="D1089" s="234"/>
-      <c r="E1089" s="235">
-        <v>195</v>
-      </c>
+      <c r="E1089" s="235"/>
       <c r="F1089" s="232"/>
       <c r="G1089" s="231"/>
       <c r="H1089" s="242"/>
@@ -27234,9 +26844,7 @@
       </c>
       <c r="C1095" s="234"/>
       <c r="D1095" s="234"/>
-      <c r="E1095" s="235">
-        <v>196</v>
-      </c>
+      <c r="E1095" s="235"/>
       <c r="F1095" s="232"/>
       <c r="G1095" s="231"/>
       <c r="H1095" s="242"/>
@@ -27248,9 +26856,7 @@
       </c>
       <c r="C1096" s="234"/>
       <c r="D1096" s="234"/>
-      <c r="E1096" s="235">
-        <v>197</v>
-      </c>
+      <c r="E1096" s="235"/>
       <c r="F1096" s="232"/>
       <c r="G1096" s="231"/>
       <c r="H1096" s="242"/>
@@ -27310,9 +26916,7 @@
       </c>
       <c r="C1100" s="234"/>
       <c r="D1100" s="234"/>
-      <c r="E1100" s="235">
-        <v>198</v>
-      </c>
+      <c r="E1100" s="235"/>
       <c r="F1100" s="232"/>
       <c r="G1100" s="231"/>
       <c r="H1100" s="242"/>
@@ -27481,7 +27085,7 @@
       </c>
     </row>
     <row r="1111" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1111" s="292" t="s">
+      <c r="B1111" s="293" t="s">
         <v>982</v>
       </c>
       <c r="C1111" s="234"/>
@@ -27497,7 +27101,7 @@
       </c>
     </row>
     <row r="1112" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1112" s="274"/>
+      <c r="B1112" s="275"/>
       <c r="C1112" s="234"/>
       <c r="D1112" s="234"/>
       <c r="E1112" s="235"/>
@@ -27511,7 +27115,7 @@
       </c>
     </row>
     <row r="1113" spans="2:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1113" s="275" t="s">
+      <c r="B1113" s="276" t="s">
         <v>978</v>
       </c>
       <c r="C1113" s="234"/>
@@ -27527,7 +27131,7 @@
       </c>
     </row>
     <row r="1114" spans="2:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1114" s="274"/>
+      <c r="B1114" s="275"/>
       <c r="C1114" s="234"/>
       <c r="D1114" s="234"/>
       <c r="E1114" s="235"/>
@@ -27541,7 +27145,7 @@
       </c>
     </row>
     <row r="1115" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1115" s="275" t="s">
+      <c r="B1115" s="276" t="s">
         <v>980</v>
       </c>
       <c r="C1115" s="234"/>
@@ -27557,7 +27161,7 @@
       </c>
     </row>
     <row r="1116" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1116" s="274"/>
+      <c r="B1116" s="275"/>
       <c r="C1116" s="234"/>
       <c r="D1116" s="234"/>
       <c r="E1116" s="235"/>
@@ -27571,7 +27175,7 @@
       </c>
     </row>
     <row r="1117" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1117" s="275" t="s">
+      <c r="B1117" s="276" t="s">
         <v>981</v>
       </c>
       <c r="C1117" s="234"/>
@@ -27587,7 +27191,7 @@
       </c>
     </row>
     <row r="1118" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1118" s="274"/>
+      <c r="B1118" s="275"/>
       <c r="C1118" s="234"/>
       <c r="D1118" s="234"/>
       <c r="E1118" s="235"/>
@@ -27796,9 +27400,7 @@
       <c r="B1131" s="161"/>
       <c r="C1131" s="234"/>
       <c r="D1131" s="234"/>
-      <c r="E1131" s="235">
-        <v>199</v>
-      </c>
+      <c r="E1131" s="235"/>
       <c r="F1131" s="232"/>
       <c r="G1131" s="231"/>
       <c r="H1131" s="242"/>
@@ -27810,9 +27412,7 @@
       </c>
       <c r="C1132" s="234"/>
       <c r="D1132" s="234"/>
-      <c r="E1132" s="235">
-        <v>200</v>
-      </c>
+      <c r="E1132" s="235"/>
       <c r="F1132" s="232"/>
       <c r="G1132" s="231"/>
       <c r="H1132" s="242"/>
@@ -27824,9 +27424,7 @@
       </c>
       <c r="C1133" s="234"/>
       <c r="D1133" s="234"/>
-      <c r="E1133" s="235">
-        <v>201</v>
-      </c>
+      <c r="E1133" s="235"/>
       <c r="F1133" s="232"/>
       <c r="G1133" s="231"/>
       <c r="H1133" s="242"/>
@@ -27854,9 +27452,7 @@
       </c>
       <c r="C1135" s="234"/>
       <c r="D1135" s="234"/>
-      <c r="E1135" s="235">
-        <v>202</v>
-      </c>
+      <c r="E1135" s="235"/>
       <c r="F1135" s="232"/>
       <c r="G1135" s="231"/>
       <c r="H1135" s="242"/>
@@ -27882,9 +27478,7 @@
       <c r="B1137" s="202"/>
       <c r="C1137" s="234"/>
       <c r="D1137" s="234"/>
-      <c r="E1137" s="235">
-        <v>203</v>
-      </c>
+      <c r="E1137" s="235"/>
       <c r="F1137" s="232"/>
       <c r="G1137" s="231"/>
       <c r="H1137" s="242"/>
@@ -27894,9 +27488,7 @@
       <c r="B1138" s="202"/>
       <c r="C1138" s="234"/>
       <c r="D1138" s="234"/>
-      <c r="E1138" s="235">
-        <v>204</v>
-      </c>
+      <c r="E1138" s="235"/>
       <c r="F1138" s="232"/>
       <c r="G1138" s="231"/>
       <c r="H1138" s="242"/>
@@ -27908,9 +27500,7 @@
       </c>
       <c r="C1139" s="234"/>
       <c r="D1139" s="234"/>
-      <c r="E1139" s="235">
-        <v>205</v>
-      </c>
+      <c r="E1139" s="235"/>
       <c r="F1139" s="232"/>
       <c r="G1139" s="231"/>
       <c r="H1139" s="242"/>
@@ -27920,9 +27510,7 @@
       <c r="B1140" s="202"/>
       <c r="C1140" s="234"/>
       <c r="D1140" s="234"/>
-      <c r="E1140" s="235">
-        <v>206</v>
-      </c>
+      <c r="E1140" s="235"/>
       <c r="F1140" s="232"/>
       <c r="G1140" s="231"/>
       <c r="H1140" s="242"/>
@@ -27934,9 +27522,7 @@
       </c>
       <c r="C1141" s="234"/>
       <c r="D1141" s="234"/>
-      <c r="E1141" s="235">
-        <v>207</v>
-      </c>
+      <c r="E1141" s="235"/>
       <c r="F1141" s="232"/>
       <c r="G1141" s="231"/>
       <c r="H1141" s="242"/>
@@ -27948,9 +27534,7 @@
       </c>
       <c r="C1142" s="234"/>
       <c r="D1142" s="234"/>
-      <c r="E1142" s="235">
-        <v>208</v>
-      </c>
+      <c r="E1142" s="235"/>
       <c r="F1142" s="232"/>
       <c r="G1142" s="231"/>
       <c r="H1142" s="242"/>
@@ -28010,9 +27594,7 @@
       </c>
       <c r="C1146" s="234"/>
       <c r="D1146" s="234"/>
-      <c r="E1146" s="235">
-        <v>209</v>
-      </c>
+      <c r="E1146" s="235"/>
       <c r="F1146" s="232"/>
       <c r="G1146" s="231"/>
       <c r="H1146" s="242"/>
@@ -28038,9 +27620,7 @@
       <c r="B1148" s="167"/>
       <c r="C1148" s="234"/>
       <c r="D1148" s="234"/>
-      <c r="E1148" s="235">
-        <v>210</v>
-      </c>
+      <c r="E1148" s="235"/>
       <c r="F1148" s="232"/>
       <c r="G1148" s="231"/>
       <c r="H1148" s="242"/>
@@ -28052,9 +27632,7 @@
       </c>
       <c r="C1149" s="234"/>
       <c r="D1149" s="234"/>
-      <c r="E1149" s="235">
-        <v>211</v>
-      </c>
+      <c r="E1149" s="235"/>
       <c r="F1149" s="232"/>
       <c r="G1149" s="231"/>
       <c r="H1149" s="242"/>
@@ -28114,9 +27692,7 @@
       </c>
       <c r="C1153" s="234"/>
       <c r="D1153" s="234"/>
-      <c r="E1153" s="235">
-        <v>212</v>
-      </c>
+      <c r="E1153" s="235"/>
       <c r="F1153" s="232"/>
       <c r="G1153" s="231"/>
       <c r="H1153" s="242"/>
@@ -28144,9 +27720,7 @@
       </c>
       <c r="C1155" s="234"/>
       <c r="D1155" s="234"/>
-      <c r="E1155" s="235">
-        <v>213</v>
-      </c>
+      <c r="E1155" s="235"/>
       <c r="F1155" s="232"/>
       <c r="G1155" s="231"/>
       <c r="H1155" s="242"/>
@@ -28174,9 +27748,7 @@
       </c>
       <c r="C1157" s="234"/>
       <c r="D1157" s="234"/>
-      <c r="E1157" s="235">
-        <v>214</v>
-      </c>
+      <c r="E1157" s="235"/>
       <c r="F1157" s="232"/>
       <c r="G1157" s="231"/>
       <c r="H1157" s="242"/>
@@ -28236,9 +27808,7 @@
       </c>
       <c r="C1161" s="234"/>
       <c r="D1161" s="234"/>
-      <c r="E1161" s="235">
-        <v>215</v>
-      </c>
+      <c r="E1161" s="235"/>
       <c r="F1161" s="232"/>
       <c r="G1161" s="231"/>
       <c r="H1161" s="242"/>
@@ -28298,9 +27868,7 @@
       </c>
       <c r="C1165" s="234"/>
       <c r="D1165" s="234"/>
-      <c r="E1165" s="235">
-        <v>216</v>
-      </c>
+      <c r="E1165" s="235"/>
       <c r="F1165" s="232"/>
       <c r="G1165" s="231"/>
       <c r="H1165" s="242"/>
@@ -28360,9 +27928,7 @@
       </c>
       <c r="C1169" s="234"/>
       <c r="D1169" s="234"/>
-      <c r="E1169" s="235">
-        <v>217</v>
-      </c>
+      <c r="E1169" s="235"/>
       <c r="F1169" s="232"/>
       <c r="G1169" s="231"/>
       <c r="H1169" s="242"/>
@@ -28422,9 +27988,7 @@
       </c>
       <c r="C1173" s="234"/>
       <c r="D1173" s="234"/>
-      <c r="E1173" s="235">
-        <v>218</v>
-      </c>
+      <c r="E1173" s="235"/>
       <c r="F1173" s="232"/>
       <c r="G1173" s="231"/>
       <c r="H1173" s="242"/>
@@ -28484,9 +28048,7 @@
       </c>
       <c r="C1177" s="234"/>
       <c r="D1177" s="234"/>
-      <c r="E1177" s="235">
-        <v>219</v>
-      </c>
+      <c r="E1177" s="235"/>
       <c r="F1177" s="232"/>
       <c r="G1177" s="231"/>
       <c r="H1177" s="242"/>
@@ -28546,9 +28108,7 @@
       </c>
       <c r="C1181" s="234"/>
       <c r="D1181" s="234"/>
-      <c r="E1181" s="235">
-        <v>220</v>
-      </c>
+      <c r="E1181" s="235"/>
       <c r="F1181" s="232"/>
       <c r="G1181" s="231"/>
       <c r="H1181" s="242"/>
@@ -28592,9 +28152,7 @@
       </c>
       <c r="C1184" s="234"/>
       <c r="D1184" s="234"/>
-      <c r="E1184" s="235">
-        <v>221</v>
-      </c>
+      <c r="E1184" s="235"/>
       <c r="F1184" s="232"/>
       <c r="G1184" s="231"/>
       <c r="H1184" s="242"/>
@@ -28654,9 +28212,7 @@
       </c>
       <c r="C1188" s="234"/>
       <c r="D1188" s="234"/>
-      <c r="E1188" s="235">
-        <v>222</v>
-      </c>
+      <c r="E1188" s="235"/>
       <c r="F1188" s="232"/>
       <c r="G1188" s="231"/>
       <c r="H1188" s="242"/>
@@ -28716,9 +28272,7 @@
       </c>
       <c r="C1192" s="234"/>
       <c r="D1192" s="234"/>
-      <c r="E1192" s="235">
-        <v>223</v>
-      </c>
+      <c r="E1192" s="235"/>
       <c r="F1192" s="232"/>
       <c r="G1192" s="231"/>
       <c r="H1192" s="242"/>
@@ -28778,9 +28332,7 @@
       </c>
       <c r="C1196" s="234"/>
       <c r="D1196" s="234"/>
-      <c r="E1196" s="235">
-        <v>224</v>
-      </c>
+      <c r="E1196" s="235"/>
       <c r="F1196" s="232"/>
       <c r="G1196" s="231"/>
       <c r="H1196" s="242"/>
@@ -28838,9 +28390,7 @@
       <c r="B1200" s="202"/>
       <c r="C1200" s="234"/>
       <c r="D1200" s="234"/>
-      <c r="E1200" s="235">
-        <v>225</v>
-      </c>
+      <c r="E1200" s="235"/>
       <c r="F1200" s="232"/>
       <c r="G1200" s="231"/>
       <c r="H1200" s="242"/>
@@ -28852,9 +28402,7 @@
       </c>
       <c r="C1201" s="234"/>
       <c r="D1201" s="234"/>
-      <c r="E1201" s="235">
-        <v>226</v>
-      </c>
+      <c r="E1201" s="235"/>
       <c r="F1201" s="232"/>
       <c r="G1201" s="231"/>
       <c r="H1201" s="242"/>
@@ -28866,9 +28414,7 @@
       </c>
       <c r="C1202" s="234"/>
       <c r="D1202" s="234"/>
-      <c r="E1202" s="235">
-        <v>227</v>
-      </c>
+      <c r="E1202" s="235"/>
       <c r="F1202" s="232"/>
       <c r="G1202" s="231"/>
       <c r="H1202" s="242"/>
@@ -28878,9 +28424,7 @@
       <c r="B1203" s="174"/>
       <c r="C1203" s="234"/>
       <c r="D1203" s="234"/>
-      <c r="E1203" s="235">
-        <v>228</v>
-      </c>
+      <c r="E1203" s="235"/>
       <c r="F1203" s="232"/>
       <c r="G1203" s="231"/>
       <c r="H1203" s="242"/>
@@ -29676,9 +29220,7 @@
       </c>
       <c r="C1253" s="234"/>
       <c r="D1253" s="234"/>
-      <c r="E1253" s="235">
-        <v>229</v>
-      </c>
+      <c r="E1253" s="235"/>
       <c r="F1253" s="232"/>
       <c r="G1253" s="231"/>
       <c r="H1253" s="242"/>
@@ -30456,9 +29998,7 @@
       <c r="B1302" s="187"/>
       <c r="C1302" s="234"/>
       <c r="D1302" s="234"/>
-      <c r="E1302" s="235">
-        <v>230</v>
-      </c>
+      <c r="E1302" s="235"/>
       <c r="F1302" s="232"/>
       <c r="G1302" s="231"/>
       <c r="H1302" s="242"/>
@@ -30470,9 +30010,7 @@
       </c>
       <c r="C1303" s="234"/>
       <c r="D1303" s="234"/>
-      <c r="E1303" s="235">
-        <v>231</v>
-      </c>
+      <c r="E1303" s="235"/>
       <c r="F1303" s="232"/>
       <c r="G1303" s="231"/>
       <c r="H1303" s="242"/>
@@ -30482,9 +30020,7 @@
       <c r="B1304" s="174"/>
       <c r="C1304" s="234"/>
       <c r="D1304" s="234"/>
-      <c r="E1304" s="235">
-        <v>232</v>
-      </c>
+      <c r="E1304" s="235"/>
       <c r="F1304" s="232"/>
       <c r="G1304" s="231"/>
       <c r="H1304" s="242"/>
@@ -31118,9 +30654,7 @@
       <c r="B1344" s="195"/>
       <c r="C1344" s="234"/>
       <c r="D1344" s="234"/>
-      <c r="E1344" s="235">
-        <v>233</v>
-      </c>
+      <c r="E1344" s="235"/>
       <c r="F1344" s="232"/>
       <c r="G1344" s="231"/>
       <c r="H1344" s="242"/>
@@ -31132,9 +30666,7 @@
       </c>
       <c r="C1345" s="234"/>
       <c r="D1345" s="234"/>
-      <c r="E1345" s="235">
-        <v>234</v>
-      </c>
+      <c r="E1345" s="235"/>
       <c r="F1345" s="232"/>
       <c r="G1345" s="231"/>
       <c r="H1345" s="242"/>
@@ -31912,9 +31444,7 @@
       <c r="B1394" s="197"/>
       <c r="C1394" s="234"/>
       <c r="D1394" s="234"/>
-      <c r="E1394" s="235">
-        <v>235</v>
-      </c>
+      <c r="E1394" s="235"/>
       <c r="F1394" s="232"/>
       <c r="G1394" s="231"/>
       <c r="H1394" s="242"/>
@@ -31926,9 +31456,7 @@
       </c>
       <c r="C1395" s="234"/>
       <c r="D1395" s="234"/>
-      <c r="E1395" s="235">
-        <v>236</v>
-      </c>
+      <c r="E1395" s="235"/>
       <c r="F1395" s="232"/>
       <c r="G1395" s="231"/>
       <c r="H1395" s="242"/>
@@ -31938,9 +31466,7 @@
       <c r="B1396" s="174"/>
       <c r="C1396" s="234"/>
       <c r="D1396" s="234"/>
-      <c r="E1396" s="235">
-        <v>237</v>
-      </c>
+      <c r="E1396" s="235"/>
       <c r="F1396" s="232"/>
       <c r="G1396" s="231"/>
       <c r="H1396" s="242"/>
@@ -31952,9 +31478,7 @@
       </c>
       <c r="C1397" s="234"/>
       <c r="D1397" s="234"/>
-      <c r="E1397" s="235">
-        <v>238</v>
-      </c>
+      <c r="E1397" s="235"/>
       <c r="F1397" s="232"/>
       <c r="G1397" s="231"/>
       <c r="H1397" s="242"/>
@@ -31982,9 +31506,7 @@
       </c>
       <c r="C1399" s="234"/>
       <c r="D1399" s="234"/>
-      <c r="E1399" s="235">
-        <v>239</v>
-      </c>
+      <c r="E1399" s="235"/>
       <c r="F1399" s="232"/>
       <c r="G1399" s="231"/>
       <c r="H1399" s="242"/>
@@ -32090,9 +31612,7 @@
       <c r="B1406" s="197"/>
       <c r="C1406" s="234"/>
       <c r="D1406" s="234"/>
-      <c r="E1406" s="235">
-        <v>240</v>
-      </c>
+      <c r="E1406" s="235"/>
       <c r="F1406" s="232"/>
       <c r="G1406" s="231"/>
       <c r="H1406" s="242"/>
@@ -32104,9 +31624,7 @@
       </c>
       <c r="C1407" s="234"/>
       <c r="D1407" s="234"/>
-      <c r="E1407" s="235">
-        <v>241</v>
-      </c>
+      <c r="E1407" s="235"/>
       <c r="F1407" s="232"/>
       <c r="G1407" s="231"/>
       <c r="H1407" s="242"/>
@@ -32116,9 +31634,7 @@
       <c r="B1408" s="174"/>
       <c r="C1408" s="234"/>
       <c r="D1408" s="234"/>
-      <c r="E1408" s="235">
-        <v>242</v>
-      </c>
+      <c r="E1408" s="235"/>
       <c r="F1408" s="232"/>
       <c r="G1408" s="231"/>
       <c r="H1408" s="242"/>
@@ -32178,9 +31694,7 @@
       </c>
       <c r="C1412" s="234"/>
       <c r="D1412" s="234"/>
-      <c r="E1412" s="235">
-        <v>243</v>
-      </c>
+      <c r="E1412" s="235"/>
       <c r="F1412" s="232"/>
       <c r="G1412" s="231"/>
       <c r="H1412" s="242"/>
@@ -32222,9 +31736,7 @@
       <c r="B1415" s="200"/>
       <c r="C1415" s="234"/>
       <c r="D1415" s="234"/>
-      <c r="E1415" s="235">
-        <v>244</v>
-      </c>
+      <c r="E1415" s="235"/>
       <c r="F1415" s="232"/>
       <c r="G1415" s="231"/>
       <c r="H1415" s="242"/>
@@ -32236,9 +31748,7 @@
       </c>
       <c r="C1416" s="234"/>
       <c r="D1416" s="234"/>
-      <c r="E1416" s="235">
-        <v>245</v>
-      </c>
+      <c r="E1416" s="235"/>
       <c r="F1416" s="232"/>
       <c r="G1416" s="231"/>
       <c r="H1416" s="242"/>
@@ -32250,9 +31760,7 @@
       </c>
       <c r="C1417" s="234"/>
       <c r="D1417" s="234"/>
-      <c r="E1417" s="235">
-        <v>246</v>
-      </c>
+      <c r="E1417" s="235"/>
       <c r="F1417" s="232"/>
       <c r="G1417" s="231"/>
       <c r="H1417" s="242"/>
@@ -32262,9 +31770,7 @@
       <c r="B1418" s="202"/>
       <c r="C1418" s="234"/>
       <c r="D1418" s="234"/>
-      <c r="E1418" s="235">
-        <v>247</v>
-      </c>
+      <c r="E1418" s="235"/>
       <c r="F1418" s="232"/>
       <c r="G1418" s="231"/>
       <c r="H1418" s="242"/>
@@ -32276,9 +31782,7 @@
       </c>
       <c r="C1419" s="234"/>
       <c r="D1419" s="234"/>
-      <c r="E1419" s="235">
-        <v>248</v>
-      </c>
+      <c r="E1419" s="235"/>
       <c r="F1419" s="232"/>
       <c r="G1419" s="231"/>
       <c r="H1419" s="242"/>
@@ -32288,9 +31792,7 @@
       <c r="B1420" s="202"/>
       <c r="C1420" s="234"/>
       <c r="D1420" s="234"/>
-      <c r="E1420" s="235">
-        <v>249</v>
-      </c>
+      <c r="E1420" s="235"/>
       <c r="F1420" s="232"/>
       <c r="G1420" s="231"/>
       <c r="H1420" s="242"/>
@@ -32380,9 +31882,7 @@
       <c r="B1426" s="202"/>
       <c r="C1426" s="234"/>
       <c r="D1426" s="234"/>
-      <c r="E1426" s="235">
-        <v>250</v>
-      </c>
+      <c r="E1426" s="235"/>
       <c r="F1426" s="232"/>
       <c r="G1426" s="231"/>
       <c r="H1426" s="242"/>
@@ -32394,9 +31894,7 @@
       </c>
       <c r="C1427" s="234"/>
       <c r="D1427" s="234"/>
-      <c r="E1427" s="235">
-        <v>251</v>
-      </c>
+      <c r="E1427" s="235"/>
       <c r="F1427" s="232"/>
       <c r="G1427" s="231"/>
       <c r="H1427" s="242"/>
@@ -32408,9 +31906,7 @@
       </c>
       <c r="C1428" s="234"/>
       <c r="D1428" s="234"/>
-      <c r="E1428" s="235">
-        <v>252</v>
-      </c>
+      <c r="E1428" s="235"/>
       <c r="F1428" s="232"/>
       <c r="G1428" s="231"/>
       <c r="H1428" s="242"/>
@@ -32454,9 +31950,7 @@
       </c>
       <c r="C1431" s="234"/>
       <c r="D1431" s="234"/>
-      <c r="E1431" s="235">
-        <v>253</v>
-      </c>
+      <c r="E1431" s="235"/>
       <c r="F1431" s="232"/>
       <c r="G1431" s="231"/>
       <c r="H1431" s="242"/>
@@ -32500,9 +31994,7 @@
       </c>
       <c r="C1434" s="234"/>
       <c r="D1434" s="234"/>
-      <c r="E1434" s="235">
-        <v>254</v>
-      </c>
+      <c r="E1434" s="235"/>
       <c r="F1434" s="232"/>
       <c r="G1434" s="231"/>
       <c r="H1434" s="242"/>
@@ -32546,9 +32038,7 @@
       </c>
       <c r="C1437" s="234"/>
       <c r="D1437" s="234"/>
-      <c r="E1437" s="235">
-        <v>255</v>
-      </c>
+      <c r="E1437" s="235"/>
       <c r="F1437" s="232"/>
       <c r="G1437" s="231"/>
       <c r="H1437" s="242"/>
@@ -32592,9 +32082,7 @@
       </c>
       <c r="C1440" s="234"/>
       <c r="D1440" s="234"/>
-      <c r="E1440" s="235">
-        <v>256</v>
-      </c>
+      <c r="E1440" s="235"/>
       <c r="F1440" s="232"/>
       <c r="G1440" s="231"/>
       <c r="H1440" s="242"/>
@@ -32638,9 +32126,7 @@
       </c>
       <c r="C1443" s="234"/>
       <c r="D1443" s="234"/>
-      <c r="E1443" s="235">
-        <v>257</v>
-      </c>
+      <c r="E1443" s="235"/>
       <c r="F1443" s="232"/>
       <c r="G1443" s="231"/>
       <c r="H1443" s="242"/>
@@ -32684,9 +32170,7 @@
       </c>
       <c r="C1446" s="234"/>
       <c r="D1446" s="234"/>
-      <c r="E1446" s="235">
-        <v>258</v>
-      </c>
+      <c r="E1446" s="235"/>
       <c r="F1446" s="232"/>
       <c r="G1446" s="231"/>
       <c r="H1446" s="242"/>
@@ -32730,9 +32214,7 @@
       </c>
       <c r="C1449" s="234"/>
       <c r="D1449" s="234"/>
-      <c r="E1449" s="235">
-        <v>259</v>
-      </c>
+      <c r="E1449" s="235"/>
       <c r="F1449" s="232"/>
       <c r="G1449" s="231"/>
       <c r="H1449" s="242"/>
@@ -32774,9 +32256,7 @@
       <c r="B1452" s="41"/>
       <c r="C1452" s="41"/>
       <c r="D1452" s="41"/>
-      <c r="E1452" s="41">
-        <v>260</v>
-      </c>
+      <c r="E1452" s="41"/>
       <c r="F1452" s="41"/>
       <c r="G1452" s="41"/>
       <c r="H1452" s="41"/>
@@ -32786,9 +32266,7 @@
       <c r="B1453" s="41"/>
       <c r="C1453" s="41"/>
       <c r="D1453" s="41"/>
-      <c r="E1453" s="41">
-        <v>261</v>
-      </c>
+      <c r="E1453" s="41"/>
       <c r="F1453" s="41"/>
       <c r="G1453" s="41"/>
       <c r="H1453" s="41"/>
@@ -32798,9 +32276,7 @@
       <c r="B1454" s="41"/>
       <c r="C1454" s="41"/>
       <c r="D1454" s="41"/>
-      <c r="E1454" s="41">
-        <v>262</v>
-      </c>
+      <c r="E1454" s="41"/>
       <c r="F1454" s="41"/>
       <c r="G1454" s="41"/>
       <c r="H1454" s="41"/>
@@ -32812,9 +32288,7 @@
       </c>
       <c r="C1455" s="54"/>
       <c r="D1455" s="54"/>
-      <c r="E1455" s="54">
-        <v>263</v>
-      </c>
+      <c r="E1455" s="54"/>
       <c r="F1455" s="54"/>
       <c r="G1455" s="54"/>
       <c r="H1455" s="54"/>
@@ -32893,74 +32367,74 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="279" t="s">
+      <c r="B2" s="280" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="295" t="s">
+      <c r="C2" s="296" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="288"/>
-      <c r="E2" s="294" t="s">
+      <c r="D2" s="289"/>
+      <c r="E2" s="295" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="294" t="s">
+      <c r="F2" s="295" t="s">
         <v>1416</v>
       </c>
-      <c r="G2" s="294" t="s">
+      <c r="G2" s="295" t="s">
         <v>1417</v>
       </c>
-      <c r="H2" s="299" t="s">
+      <c r="H2" s="300" t="s">
         <v>1418</v>
       </c>
-      <c r="I2" s="300"/>
-      <c r="J2" s="294" t="s">
+      <c r="I2" s="301"/>
+      <c r="J2" s="295" t="s">
         <v>1419</v>
       </c>
-      <c r="K2" s="294" t="s">
+      <c r="K2" s="295" t="s">
         <v>1420</v>
       </c>
-      <c r="L2" s="294" t="s">
+      <c r="L2" s="295" t="s">
         <v>1421</v>
       </c>
-      <c r="M2" s="294" t="s">
+      <c r="M2" s="295" t="s">
         <v>1422</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="280"/>
-      <c r="C3" s="298" t="s">
+      <c r="B3" s="281"/>
+      <c r="C3" s="299" t="s">
         <v>1423</v>
       </c>
-      <c r="D3" s="298" t="s">
+      <c r="D3" s="299" t="s">
         <v>1424</v>
       </c>
-      <c r="E3" s="271"/>
-      <c r="F3" s="271"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="301"/>
-      <c r="I3" s="302"/>
-      <c r="J3" s="271"/>
-      <c r="K3" s="271"/>
-      <c r="L3" s="271"/>
-      <c r="M3" s="271"/>
+      <c r="E3" s="272"/>
+      <c r="F3" s="272"/>
+      <c r="G3" s="272"/>
+      <c r="H3" s="302"/>
+      <c r="I3" s="303"/>
+      <c r="J3" s="272"/>
+      <c r="K3" s="272"/>
+      <c r="L3" s="272"/>
+      <c r="M3" s="272"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="274"/>
-      <c r="C4" s="272"/>
-      <c r="D4" s="272"/>
-      <c r="E4" s="272"/>
-      <c r="F4" s="272"/>
-      <c r="G4" s="272"/>
+      <c r="B4" s="275"/>
+      <c r="C4" s="273"/>
+      <c r="D4" s="273"/>
+      <c r="E4" s="273"/>
+      <c r="F4" s="273"/>
+      <c r="G4" s="273"/>
       <c r="H4" s="244" t="s">
         <v>1425</v>
       </c>
       <c r="I4" s="244" t="s">
         <v>1426</v>
       </c>
-      <c r="J4" s="272"/>
-      <c r="K4" s="272"/>
-      <c r="L4" s="272"/>
-      <c r="M4" s="272"/>
+      <c r="J4" s="273"/>
+      <c r="K4" s="273"/>
+      <c r="L4" s="273"/>
+      <c r="M4" s="273"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="246" t="s">
@@ -33006,7 +32480,7 @@
         <f>G8/J8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L8" s="296"/>
+      <c r="L8" s="297"/>
       <c r="M8" t="s">
         <v>1430</v>
       </c>
@@ -33035,7 +32509,7 @@
         <f>G9/J9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L9" s="297"/>
+      <c r="L9" s="298"/>
       <c r="M9" t="s">
         <v>1430</v>
       </c>
@@ -33076,52 +32550,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="279" t="s">
+      <c r="B2" s="280" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="287" t="s">
+      <c r="C2" s="288" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="288"/>
-      <c r="E2" s="288"/>
-      <c r="F2" s="288"/>
-      <c r="G2" s="288"/>
-      <c r="H2" s="289"/>
-      <c r="I2" s="270" t="s">
+      <c r="D2" s="289"/>
+      <c r="E2" s="289"/>
+      <c r="F2" s="289"/>
+      <c r="G2" s="289"/>
+      <c r="H2" s="290"/>
+      <c r="I2" s="271" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="280"/>
-      <c r="C3" s="284" t="s">
+      <c r="B3" s="281"/>
+      <c r="C3" s="285" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="276" t="s">
+      <c r="D3" s="277" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="276" t="s">
+      <c r="E3" s="277" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="276" t="s">
+      <c r="F3" s="277" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="276" t="s">
+      <c r="G3" s="277" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="276" t="s">
+      <c r="H3" s="277" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="271"/>
+      <c r="I3" s="272"/>
     </row>
     <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="274"/>
-      <c r="C4" s="285"/>
-      <c r="D4" s="272"/>
-      <c r="E4" s="272"/>
-      <c r="F4" s="272"/>
-      <c r="G4" s="272"/>
-      <c r="H4" s="272"/>
-      <c r="I4" s="272"/>
+      <c r="B4" s="275"/>
+      <c r="C4" s="286"/>
+      <c r="D4" s="273"/>
+      <c r="E4" s="273"/>
+      <c r="F4" s="273"/>
+      <c r="G4" s="273"/>
+      <c r="H4" s="273"/>
+      <c r="I4" s="273"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C6" s="234"/>
@@ -33136,9 +32610,7 @@
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C7" s="234"/>
       <c r="D7" s="234"/>
-      <c r="E7" s="235">
-        <v>1</v>
-      </c>
+      <c r="E7" s="235"/>
       <c r="F7" s="232"/>
       <c r="G7" s="231"/>
       <c r="H7" s="242"/>
@@ -33146,9 +32618,7 @@
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C8" s="234"/>
       <c r="D8" s="234"/>
-      <c r="E8" s="235">
-        <v>2</v>
-      </c>
+      <c r="E8" s="235"/>
       <c r="F8" s="232"/>
       <c r="G8" s="231"/>
       <c r="H8" s="242"/>
@@ -33197,9 +32667,7 @@
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C13" s="234"/>
       <c r="D13" s="234"/>
-      <c r="E13" s="235">
-        <v>3</v>
-      </c>
+      <c r="E13" s="235"/>
       <c r="F13" s="232"/>
       <c r="G13" s="231"/>
       <c r="H13" s="242"/>
@@ -33207,9 +32675,7 @@
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C14" s="234"/>
       <c r="D14" s="234"/>
-      <c r="E14" s="235">
-        <v>4</v>
-      </c>
+      <c r="E14" s="235"/>
       <c r="F14" s="232"/>
       <c r="G14" s="231"/>
       <c r="H14" s="242"/>
@@ -33217,9 +32683,7 @@
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C15" s="234"/>
       <c r="D15" s="234"/>
-      <c r="E15" s="235">
-        <v>5</v>
-      </c>
+      <c r="E15" s="235"/>
       <c r="F15" s="232"/>
       <c r="G15" s="231"/>
       <c r="H15" s="242"/>
@@ -33274,57 +32738,57 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="311" t="s">
+      <c r="A2" s="312" t="s">
         <v>1440</v>
       </c>
-      <c r="B2" s="308" t="s">
+      <c r="B2" s="309" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="287" t="s">
+      <c r="C2" s="288" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="288"/>
-      <c r="E2" s="288"/>
-      <c r="F2" s="288"/>
-      <c r="G2" s="288"/>
-      <c r="H2" s="289"/>
-      <c r="I2" s="270" t="s">
+      <c r="D2" s="289"/>
+      <c r="E2" s="289"/>
+      <c r="F2" s="289"/>
+      <c r="G2" s="289"/>
+      <c r="H2" s="290"/>
+      <c r="I2" s="271" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="271"/>
-      <c r="B3" s="280"/>
-      <c r="C3" s="284" t="s">
+      <c r="A3" s="272"/>
+      <c r="B3" s="281"/>
+      <c r="C3" s="285" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="276" t="s">
+      <c r="D3" s="277" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="276" t="s">
+      <c r="E3" s="277" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="276" t="s">
+      <c r="F3" s="277" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="276" t="s">
+      <c r="G3" s="277" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="276" t="s">
+      <c r="H3" s="277" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="271"/>
+      <c r="I3" s="272"/>
     </row>
     <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="272"/>
-      <c r="B4" s="274"/>
-      <c r="C4" s="285"/>
-      <c r="D4" s="272"/>
-      <c r="E4" s="272"/>
-      <c r="F4" s="272"/>
-      <c r="G4" s="272"/>
-      <c r="H4" s="272"/>
-      <c r="I4" s="272"/>
+      <c r="A4" s="273"/>
+      <c r="B4" s="275"/>
+      <c r="C4" s="286"/>
+      <c r="D4" s="273"/>
+      <c r="E4" s="273"/>
+      <c r="F4" s="273"/>
+      <c r="G4" s="273"/>
+      <c r="H4" s="273"/>
+      <c r="I4" s="273"/>
     </row>
     <row r="5" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="35"/>
@@ -33361,10 +32825,10 @@
       <c r="I6" s="257"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="304" t="s">
+      <c r="A7" s="305" t="s">
         <v>1446</v>
       </c>
-      <c r="B7" s="305" t="s">
+      <c r="B7" s="306" t="s">
         <v>1447</v>
       </c>
       <c r="C7" s="234" t="s">
@@ -33378,8 +32842,8 @@
       <c r="I7" s="257"/>
     </row>
     <row r="8" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="271"/>
-      <c r="B8" s="271"/>
+      <c r="A8" s="272"/>
+      <c r="B8" s="272"/>
       <c r="C8" s="234" t="s">
         <v>1449</v>
       </c>
@@ -33467,10 +32931,10 @@
       <c r="I12" s="257"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="307" t="s">
+      <c r="A13" s="308" t="s">
         <v>1464</v>
       </c>
-      <c r="B13" s="310" t="s">
+      <c r="B13" s="311" t="s">
         <v>1465</v>
       </c>
       <c r="C13" s="234" t="s">
@@ -33484,8 +32948,8 @@
       <c r="I13" s="257"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="271"/>
-      <c r="B14" s="271"/>
+      <c r="A14" s="272"/>
+      <c r="B14" s="272"/>
       <c r="C14" s="234" t="s">
         <v>1467</v>
       </c>
@@ -33533,10 +32997,10 @@
       <c r="I16" s="257"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="304" t="s">
+      <c r="A17" s="305" t="s">
         <v>1474</v>
       </c>
-      <c r="B17" s="309" t="s">
+      <c r="B17" s="310" t="s">
         <v>1475</v>
       </c>
       <c r="C17" s="234" t="s">
@@ -33550,8 +33014,8 @@
       <c r="I17" s="257"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="271"/>
-      <c r="B18" s="271"/>
+      <c r="A18" s="272"/>
+      <c r="B18" s="272"/>
       <c r="C18" s="234" t="s">
         <v>1477</v>
       </c>
@@ -33673,9 +33137,7 @@
       </c>
       <c r="C25" s="234"/>
       <c r="D25" s="234"/>
-      <c r="E25" s="235">
-        <v>1</v>
-      </c>
+      <c r="E25" s="235"/>
       <c r="F25" s="232"/>
       <c r="G25" s="236"/>
       <c r="H25" s="243"/>
@@ -33724,9 +33186,7 @@
       </c>
       <c r="C28" s="234"/>
       <c r="D28" s="234"/>
-      <c r="E28" s="235">
-        <v>6</v>
-      </c>
+      <c r="E28" s="235"/>
       <c r="F28" s="232"/>
       <c r="G28" s="236"/>
       <c r="H28" s="243"/>
@@ -33750,10 +33210,10 @@
       <c r="I29" s="257"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="304" t="s">
+      <c r="A30" s="305" t="s">
         <v>1505</v>
       </c>
-      <c r="B30" s="309" t="s">
+      <c r="B30" s="310" t="s">
         <v>1506</v>
       </c>
       <c r="C30" s="234" t="s">
@@ -33767,8 +33227,8 @@
       <c r="I30" s="257"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="271"/>
-      <c r="B31" s="271"/>
+      <c r="A31" s="272"/>
+      <c r="B31" s="272"/>
       <c r="C31" s="234" t="s">
         <v>1508</v>
       </c>
@@ -33780,10 +33240,10 @@
       <c r="I31" s="257"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="303" t="s">
+      <c r="A32" s="304" t="s">
         <v>1509</v>
       </c>
-      <c r="B32" s="306" t="s">
+      <c r="B32" s="307" t="s">
         <v>1510</v>
       </c>
       <c r="C32" s="234" t="s">
@@ -33797,8 +33257,8 @@
       <c r="I32" s="257"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="271"/>
-      <c r="B33" s="271"/>
+      <c r="A33" s="272"/>
+      <c r="B33" s="272"/>
       <c r="C33" s="234" t="s">
         <v>1512</v>
       </c>
@@ -33813,7 +33273,7 @@
       <c r="A34" s="266" t="s">
         <v>1513</v>
       </c>
-      <c r="B34" s="306" t="s">
+      <c r="B34" s="307" t="s">
         <v>1514</v>
       </c>
       <c r="C34" s="234" t="s">
@@ -33828,7 +33288,7 @@
     </row>
     <row r="35" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="266"/>
-      <c r="B35" s="271"/>
+      <c r="B35" s="272"/>
       <c r="C35" s="234" t="s">
         <v>1516</v>
       </c>
@@ -33843,7 +33303,7 @@
       <c r="A36" s="266" t="s">
         <v>1517</v>
       </c>
-      <c r="B36" s="306" t="s">
+      <c r="B36" s="307" t="s">
         <v>1518</v>
       </c>
       <c r="C36" s="234" t="s">
@@ -33858,7 +33318,7 @@
     </row>
     <row r="37" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="266"/>
-      <c r="B37" s="271"/>
+      <c r="B37" s="272"/>
       <c r="C37" s="234" t="s">
         <v>1520</v>
       </c>
@@ -33995,9 +33455,7 @@
       </c>
       <c r="C45" s="234"/>
       <c r="D45" s="234"/>
-      <c r="E45" s="235">
-        <v>2</v>
-      </c>
+      <c r="E45" s="235"/>
       <c r="F45" s="232"/>
       <c r="G45" s="236"/>
       <c r="H45" s="243"/>
@@ -34104,9 +33562,7 @@
       </c>
       <c r="C52" s="234"/>
       <c r="D52" s="234"/>
-      <c r="E52" s="235">
-        <v>3</v>
-      </c>
+      <c r="E52" s="235"/>
       <c r="F52" s="232"/>
       <c r="G52" s="236"/>
       <c r="H52" s="243"/>
@@ -34245,9 +33701,7 @@
       </c>
       <c r="C61" s="234"/>
       <c r="D61" s="234"/>
-      <c r="E61" s="235">
-        <v>4</v>
-      </c>
+      <c r="E61" s="235"/>
       <c r="F61" s="232"/>
       <c r="G61" s="236"/>
       <c r="H61" s="243"/>
@@ -34450,10 +33904,10 @@
       <c r="I73" s="257"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="304" t="s">
+      <c r="A74" s="305" t="s">
         <v>1598</v>
       </c>
-      <c r="B74" s="305" t="s">
+      <c r="B74" s="306" t="s">
         <v>1599</v>
       </c>
       <c r="C74" s="234" t="s">
@@ -34467,8 +33921,8 @@
       <c r="I74" s="257"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="271"/>
-      <c r="B75" s="271"/>
+      <c r="A75" s="272"/>
+      <c r="B75" s="272"/>
       <c r="C75" s="234" t="s">
         <v>1601</v>
       </c>
@@ -34520,9 +33974,7 @@
       </c>
       <c r="C78" s="234"/>
       <c r="D78" s="234"/>
-      <c r="E78" s="235">
-        <v>5</v>
-      </c>
+      <c r="E78" s="235"/>
       <c r="F78" s="232"/>
       <c r="G78" s="236"/>
       <c r="H78" s="243"/>
@@ -34666,57 +34118,57 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="311" t="s">
+      <c r="A2" s="312" t="s">
         <v>1440</v>
       </c>
-      <c r="B2" s="270" t="s">
+      <c r="B2" s="271" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="287" t="s">
+      <c r="C2" s="288" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="288"/>
-      <c r="E2" s="288"/>
-      <c r="F2" s="288"/>
-      <c r="G2" s="288"/>
-      <c r="H2" s="289"/>
-      <c r="I2" s="270" t="s">
+      <c r="D2" s="289"/>
+      <c r="E2" s="289"/>
+      <c r="F2" s="289"/>
+      <c r="G2" s="289"/>
+      <c r="H2" s="290"/>
+      <c r="I2" s="271" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="271"/>
-      <c r="B3" s="271"/>
-      <c r="C3" s="284" t="s">
+      <c r="A3" s="272"/>
+      <c r="B3" s="272"/>
+      <c r="C3" s="285" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="276" t="s">
+      <c r="D3" s="277" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="276" t="s">
+      <c r="E3" s="277" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="276" t="s">
+      <c r="F3" s="277" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="276" t="s">
+      <c r="G3" s="277" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="276" t="s">
+      <c r="H3" s="277" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="271"/>
+      <c r="I3" s="272"/>
     </row>
     <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="272"/>
-      <c r="B4" s="272"/>
-      <c r="C4" s="285"/>
-      <c r="D4" s="272"/>
-      <c r="E4" s="272"/>
-      <c r="F4" s="272"/>
-      <c r="G4" s="272"/>
-      <c r="H4" s="272"/>
-      <c r="I4" s="272"/>
+      <c r="A4" s="273"/>
+      <c r="B4" s="273"/>
+      <c r="C4" s="286"/>
+      <c r="D4" s="273"/>
+      <c r="E4" s="273"/>
+      <c r="F4" s="273"/>
+      <c r="G4" s="273"/>
+      <c r="H4" s="273"/>
+      <c r="I4" s="273"/>
     </row>
     <row r="5" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="35"/>
@@ -34742,10 +34194,10 @@
       <c r="H6" s="242"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="304" t="s">
+      <c r="A7" s="305" t="s">
         <v>1446</v>
       </c>
-      <c r="B7" s="305" t="s">
+      <c r="B7" s="306" t="s">
         <v>1447</v>
       </c>
       <c r="C7" s="234" t="s">
@@ -34758,8 +34210,8 @@
       <c r="H7" s="242"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="271"/>
-      <c r="B8" s="271"/>
+      <c r="A8" s="272"/>
+      <c r="B8" s="272"/>
       <c r="C8" s="234" t="s">
         <v>1622</v>
       </c>
@@ -34830,10 +34282,10 @@
       <c r="H12" s="242"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="307" t="s">
+      <c r="A13" s="308" t="s">
         <v>1464</v>
       </c>
-      <c r="B13" s="310" t="s">
+      <c r="B13" s="311" t="s">
         <v>1465</v>
       </c>
       <c r="C13" s="234" t="s">
@@ -34846,8 +34298,8 @@
       <c r="H13" s="242"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="271"/>
-      <c r="B14" s="271"/>
+      <c r="A14" s="272"/>
+      <c r="B14" s="272"/>
       <c r="C14" s="234" t="s">
         <v>1628</v>
       </c>
@@ -34890,10 +34342,10 @@
       <c r="H16" s="242"/>
     </row>
     <row r="17" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="304" t="s">
+      <c r="A17" s="305" t="s">
         <v>1474</v>
       </c>
-      <c r="B17" s="309" t="s">
+      <c r="B17" s="310" t="s">
         <v>1475</v>
       </c>
       <c r="C17" s="234" t="s">
@@ -34908,8 +34360,8 @@
       <c r="H17" s="242"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="271"/>
-      <c r="B18" s="271"/>
+      <c r="A18" s="272"/>
+      <c r="B18" s="272"/>
       <c r="C18" s="234"/>
       <c r="D18" s="234" t="s">
         <v>1633</v>
@@ -34930,9 +34382,7 @@
       </c>
       <c r="C19" s="234"/>
       <c r="D19" s="234"/>
-      <c r="E19" s="235">
-        <v>1</v>
-      </c>
+      <c r="E19" s="235"/>
       <c r="F19" s="232"/>
       <c r="G19" s="231"/>
       <c r="H19" s="242"/>
@@ -34946,9 +34396,7 @@
       </c>
       <c r="C20" s="234"/>
       <c r="D20" s="234"/>
-      <c r="E20" s="235">
-        <v>2</v>
-      </c>
+      <c r="E20" s="235"/>
       <c r="F20" s="232"/>
       <c r="G20" s="231"/>
       <c r="H20" s="242"/>
@@ -34962,9 +34410,7 @@
       </c>
       <c r="C21" s="234"/>
       <c r="D21" s="234"/>
-      <c r="E21" s="235">
-        <v>3</v>
-      </c>
+      <c r="E21" s="235"/>
       <c r="F21" s="232"/>
       <c r="G21" s="231"/>
       <c r="H21" s="242"/>
@@ -34978,9 +34424,7 @@
       </c>
       <c r="C22" s="234"/>
       <c r="D22" s="234"/>
-      <c r="E22" s="235">
-        <v>4</v>
-      </c>
+      <c r="E22" s="235"/>
       <c r="F22" s="232"/>
       <c r="G22" s="231"/>
       <c r="H22" s="242"/>
@@ -34994,9 +34438,7 @@
       </c>
       <c r="C23" s="234"/>
       <c r="D23" s="234"/>
-      <c r="E23" s="235">
-        <v>5</v>
-      </c>
+      <c r="E23" s="235"/>
       <c r="F23" s="232"/>
       <c r="G23" s="231"/>
       <c r="H23" s="242"/>
@@ -35010,9 +34452,7 @@
       </c>
       <c r="C24" s="234"/>
       <c r="D24" s="234"/>
-      <c r="E24" s="235">
-        <v>6</v>
-      </c>
+      <c r="E24" s="235"/>
       <c r="F24" s="232"/>
       <c r="G24" s="231"/>
       <c r="H24" s="242"/>
@@ -35024,9 +34464,7 @@
       </c>
       <c r="C25" s="234"/>
       <c r="D25" s="234"/>
-      <c r="E25" s="235">
-        <v>7</v>
-      </c>
+      <c r="E25" s="235"/>
       <c r="F25" s="232"/>
       <c r="G25" s="231"/>
       <c r="H25" s="242"/>
@@ -35040,9 +34478,7 @@
       </c>
       <c r="C26" s="234"/>
       <c r="D26" s="234"/>
-      <c r="E26" s="235">
-        <v>8</v>
-      </c>
+      <c r="E26" s="235"/>
       <c r="F26" s="232"/>
       <c r="G26" s="231"/>
       <c r="H26" s="242"/>
@@ -35056,9 +34492,7 @@
       </c>
       <c r="C27" s="234"/>
       <c r="D27" s="234"/>
-      <c r="E27" s="235">
-        <v>9</v>
-      </c>
+      <c r="E27" s="235"/>
       <c r="F27" s="232"/>
       <c r="G27" s="231"/>
       <c r="H27" s="242"/>
@@ -35072,9 +34506,7 @@
       </c>
       <c r="C28" s="234"/>
       <c r="D28" s="234"/>
-      <c r="E28" s="235">
-        <v>10</v>
-      </c>
+      <c r="E28" s="235"/>
       <c r="F28" s="232"/>
       <c r="G28" s="231"/>
       <c r="H28" s="242"/>
@@ -35088,65 +34520,55 @@
       </c>
       <c r="C29" s="234"/>
       <c r="D29" s="234"/>
-      <c r="E29" s="235">
-        <v>11</v>
-      </c>
+      <c r="E29" s="235"/>
       <c r="F29" s="232"/>
       <c r="G29" s="231"/>
       <c r="H29" s="242"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="304" t="s">
+      <c r="A30" s="305" t="s">
         <v>1505</v>
       </c>
-      <c r="B30" s="309" t="s">
+      <c r="B30" s="310" t="s">
         <v>1506</v>
       </c>
       <c r="C30" s="234"/>
       <c r="D30" s="234"/>
-      <c r="E30" s="235">
-        <v>12</v>
-      </c>
+      <c r="E30" s="235"/>
       <c r="F30" s="232"/>
       <c r="G30" s="231"/>
       <c r="H30" s="242"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="271"/>
-      <c r="B31" s="271"/>
+      <c r="A31" s="272"/>
+      <c r="B31" s="272"/>
       <c r="C31" s="234"/>
       <c r="D31" s="234"/>
-      <c r="E31" s="235">
-        <v>13</v>
-      </c>
+      <c r="E31" s="235"/>
       <c r="F31" s="232"/>
       <c r="G31" s="231"/>
       <c r="H31" s="242"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="303" t="s">
+      <c r="A32" s="304" t="s">
         <v>1509</v>
       </c>
-      <c r="B32" s="306" t="s">
+      <c r="B32" s="307" t="s">
         <v>1510</v>
       </c>
       <c r="C32" s="234"/>
       <c r="D32" s="234"/>
-      <c r="E32" s="235">
-        <v>14</v>
-      </c>
+      <c r="E32" s="235"/>
       <c r="F32" s="232"/>
       <c r="G32" s="231"/>
       <c r="H32" s="242"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="271"/>
-      <c r="B33" s="271"/>
+      <c r="A33" s="272"/>
+      <c r="B33" s="272"/>
       <c r="C33" s="234"/>
       <c r="D33" s="234"/>
-      <c r="E33" s="235">
-        <v>15</v>
-      </c>
+      <c r="E33" s="235"/>
       <c r="F33" s="232"/>
       <c r="G33" s="231"/>
       <c r="H33" s="242"/>
@@ -35155,26 +34577,22 @@
       <c r="A34" s="266" t="s">
         <v>1513</v>
       </c>
-      <c r="B34" s="314" t="s">
+      <c r="B34" s="315" t="s">
         <v>1514</v>
       </c>
       <c r="C34" s="234"/>
       <c r="D34" s="234"/>
-      <c r="E34" s="235">
-        <v>16</v>
-      </c>
+      <c r="E34" s="235"/>
       <c r="F34" s="232"/>
       <c r="G34" s="231"/>
       <c r="H34" s="242"/>
     </row>
     <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="266"/>
-      <c r="B35" s="313"/>
+      <c r="B35" s="314"/>
       <c r="C35" s="234"/>
       <c r="D35" s="234"/>
-      <c r="E35" s="235">
-        <v>17</v>
-      </c>
+      <c r="E35" s="235"/>
       <c r="F35" s="232"/>
       <c r="G35" s="231"/>
       <c r="H35" s="242"/>
@@ -35183,26 +34601,22 @@
       <c r="A36" s="266" t="s">
         <v>1517</v>
       </c>
-      <c r="B36" s="306" t="s">
+      <c r="B36" s="307" t="s">
         <v>1518</v>
       </c>
       <c r="C36" s="234"/>
       <c r="D36" s="234"/>
-      <c r="E36" s="235">
-        <v>18</v>
-      </c>
+      <c r="E36" s="235"/>
       <c r="F36" s="232"/>
       <c r="G36" s="231"/>
       <c r="H36" s="242"/>
     </row>
     <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="266"/>
-      <c r="B37" s="271"/>
+      <c r="B37" s="272"/>
       <c r="C37" s="234"/>
       <c r="D37" s="234"/>
-      <c r="E37" s="235">
-        <v>19</v>
-      </c>
+      <c r="E37" s="235"/>
       <c r="F37" s="232"/>
       <c r="G37" s="231"/>
       <c r="H37" s="242"/>
@@ -35216,9 +34630,7 @@
       </c>
       <c r="C38" s="234"/>
       <c r="D38" s="234"/>
-      <c r="E38" s="235">
-        <v>20</v>
-      </c>
+      <c r="E38" s="235"/>
       <c r="F38" s="232"/>
       <c r="G38" s="231"/>
       <c r="H38" s="242"/>
@@ -35232,9 +34644,7 @@
       </c>
       <c r="C39" s="234"/>
       <c r="D39" s="234"/>
-      <c r="E39" s="235">
-        <v>21</v>
-      </c>
+      <c r="E39" s="235"/>
       <c r="F39" s="232"/>
       <c r="G39" s="231"/>
       <c r="H39" s="242"/>
@@ -35248,9 +34658,7 @@
       </c>
       <c r="C40" s="234"/>
       <c r="D40" s="234"/>
-      <c r="E40" s="235">
-        <v>22</v>
-      </c>
+      <c r="E40" s="235"/>
       <c r="F40" s="232"/>
       <c r="G40" s="231"/>
       <c r="H40" s="242"/>
@@ -35264,9 +34672,7 @@
       </c>
       <c r="C41" s="234"/>
       <c r="D41" s="234"/>
-      <c r="E41" s="235">
-        <v>23</v>
-      </c>
+      <c r="E41" s="235"/>
       <c r="F41" s="232"/>
       <c r="G41" s="231"/>
       <c r="H41" s="242"/>
@@ -35280,9 +34686,7 @@
       </c>
       <c r="C42" s="234"/>
       <c r="D42" s="234"/>
-      <c r="E42" s="235">
-        <v>24</v>
-      </c>
+      <c r="E42" s="235"/>
       <c r="F42" s="232"/>
       <c r="G42" s="231"/>
       <c r="H42" s="242"/>
@@ -35296,9 +34700,7 @@
       </c>
       <c r="C43" s="234"/>
       <c r="D43" s="234"/>
-      <c r="E43" s="235">
-        <v>25</v>
-      </c>
+      <c r="E43" s="235"/>
       <c r="F43" s="232"/>
       <c r="G43" s="231"/>
       <c r="H43" s="242"/>
@@ -35312,9 +34714,7 @@
       </c>
       <c r="C44" s="234"/>
       <c r="D44" s="234"/>
-      <c r="E44" s="235">
-        <v>26</v>
-      </c>
+      <c r="E44" s="235"/>
       <c r="F44" s="232"/>
       <c r="G44" s="231"/>
       <c r="H44" s="242"/>
@@ -35326,9 +34726,7 @@
       </c>
       <c r="C45" s="234"/>
       <c r="D45" s="234"/>
-      <c r="E45" s="235">
-        <v>27</v>
-      </c>
+      <c r="E45" s="235"/>
       <c r="F45" s="232"/>
       <c r="G45" s="231"/>
       <c r="H45" s="242"/>
@@ -35340,9 +34738,7 @@
       </c>
       <c r="C46" s="234"/>
       <c r="D46" s="234"/>
-      <c r="E46" s="235">
-        <v>28</v>
-      </c>
+      <c r="E46" s="235"/>
       <c r="F46" s="232"/>
       <c r="G46" s="231"/>
       <c r="H46" s="242"/>
@@ -35354,9 +34750,7 @@
       </c>
       <c r="C47" s="234"/>
       <c r="D47" s="234"/>
-      <c r="E47" s="235">
-        <v>29</v>
-      </c>
+      <c r="E47" s="235"/>
       <c r="F47" s="232"/>
       <c r="G47" s="231"/>
       <c r="H47" s="242"/>
@@ -35368,9 +34762,7 @@
       </c>
       <c r="C48" s="234"/>
       <c r="D48" s="234"/>
-      <c r="E48" s="235">
-        <v>30</v>
-      </c>
+      <c r="E48" s="235"/>
       <c r="F48" s="232"/>
       <c r="G48" s="231"/>
       <c r="H48" s="242"/>
@@ -35384,9 +34776,7 @@
       </c>
       <c r="C49" s="234"/>
       <c r="D49" s="234"/>
-      <c r="E49" s="235">
-        <v>31</v>
-      </c>
+      <c r="E49" s="235"/>
       <c r="F49" s="232"/>
       <c r="G49" s="231"/>
       <c r="H49" s="242"/>
@@ -35400,9 +34790,7 @@
       </c>
       <c r="C50" s="234"/>
       <c r="D50" s="234"/>
-      <c r="E50" s="235">
-        <v>32</v>
-      </c>
+      <c r="E50" s="235"/>
       <c r="F50" s="232"/>
       <c r="G50" s="231"/>
       <c r="H50" s="242"/>
@@ -35414,9 +34802,7 @@
       </c>
       <c r="C51" s="234"/>
       <c r="D51" s="234"/>
-      <c r="E51" s="235">
-        <v>33</v>
-      </c>
+      <c r="E51" s="235"/>
       <c r="F51" s="232"/>
       <c r="G51" s="231"/>
       <c r="H51" s="242"/>
@@ -35428,9 +34814,7 @@
       </c>
       <c r="C52" s="234"/>
       <c r="D52" s="234"/>
-      <c r="E52" s="235">
-        <v>34</v>
-      </c>
+      <c r="E52" s="235"/>
       <c r="F52" s="232"/>
       <c r="G52" s="231"/>
       <c r="H52" s="242"/>
@@ -35442,9 +34826,7 @@
       </c>
       <c r="C53" s="234"/>
       <c r="D53" s="234"/>
-      <c r="E53" s="235">
-        <v>35</v>
-      </c>
+      <c r="E53" s="235"/>
       <c r="F53" s="232"/>
       <c r="G53" s="231"/>
       <c r="H53" s="242"/>
@@ -35456,9 +34838,7 @@
       </c>
       <c r="C54" s="234"/>
       <c r="D54" s="234"/>
-      <c r="E54" s="235">
-        <v>36</v>
-      </c>
+      <c r="E54" s="235"/>
       <c r="F54" s="232"/>
       <c r="G54" s="231"/>
       <c r="H54" s="242"/>
@@ -35470,9 +34850,7 @@
       </c>
       <c r="C55" s="234"/>
       <c r="D55" s="234"/>
-      <c r="E55" s="235">
-        <v>37</v>
-      </c>
+      <c r="E55" s="235"/>
       <c r="F55" s="232"/>
       <c r="G55" s="231"/>
       <c r="H55" s="242"/>
@@ -35484,9 +34862,7 @@
       </c>
       <c r="C56" s="234"/>
       <c r="D56" s="234"/>
-      <c r="E56" s="235">
-        <v>38</v>
-      </c>
+      <c r="E56" s="235"/>
       <c r="F56" s="232"/>
       <c r="G56" s="231"/>
       <c r="H56" s="242"/>
@@ -35498,9 +34874,7 @@
       </c>
       <c r="C57" s="234"/>
       <c r="D57" s="234"/>
-      <c r="E57" s="235">
-        <v>39</v>
-      </c>
+      <c r="E57" s="235"/>
       <c r="F57" s="232"/>
       <c r="G57" s="231"/>
       <c r="H57" s="242"/>
@@ -35514,9 +34888,7 @@
       </c>
       <c r="C58" s="234"/>
       <c r="D58" s="234"/>
-      <c r="E58" s="235">
-        <v>40</v>
-      </c>
+      <c r="E58" s="235"/>
       <c r="F58" s="232"/>
       <c r="G58" s="231"/>
       <c r="H58" s="242"/>
@@ -35530,9 +34902,7 @@
       </c>
       <c r="C59" s="234"/>
       <c r="D59" s="234"/>
-      <c r="E59" s="235">
-        <v>41</v>
-      </c>
+      <c r="E59" s="235"/>
       <c r="F59" s="232"/>
       <c r="G59" s="231"/>
       <c r="H59" s="242"/>
@@ -35546,9 +34916,7 @@
       </c>
       <c r="C60" s="234"/>
       <c r="D60" s="234"/>
-      <c r="E60" s="235">
-        <v>42</v>
-      </c>
+      <c r="E60" s="235"/>
       <c r="F60" s="232"/>
       <c r="G60" s="231"/>
       <c r="H60" s="242"/>
@@ -35560,9 +34928,7 @@
       </c>
       <c r="C61" s="234"/>
       <c r="D61" s="234"/>
-      <c r="E61" s="235">
-        <v>43</v>
-      </c>
+      <c r="E61" s="235"/>
       <c r="F61" s="232"/>
       <c r="G61" s="231"/>
       <c r="H61" s="242"/>
@@ -35574,9 +34940,7 @@
       </c>
       <c r="C62" s="234"/>
       <c r="D62" s="234"/>
-      <c r="E62" s="235">
-        <v>44</v>
-      </c>
+      <c r="E62" s="235"/>
       <c r="F62" s="232"/>
       <c r="G62" s="231"/>
       <c r="H62" s="242"/>
@@ -35588,9 +34952,7 @@
       </c>
       <c r="C63" s="234"/>
       <c r="D63" s="234"/>
-      <c r="E63" s="235">
-        <v>45</v>
-      </c>
+      <c r="E63" s="235"/>
       <c r="F63" s="232"/>
       <c r="G63" s="231"/>
       <c r="H63" s="242"/>
@@ -35602,9 +34964,7 @@
       </c>
       <c r="C64" s="234"/>
       <c r="D64" s="234"/>
-      <c r="E64" s="235">
-        <v>46</v>
-      </c>
+      <c r="E64" s="235"/>
       <c r="F64" s="232"/>
       <c r="G64" s="231"/>
       <c r="H64" s="242"/>
@@ -35618,9 +34978,7 @@
       </c>
       <c r="C65" s="234"/>
       <c r="D65" s="234"/>
-      <c r="E65" s="235">
-        <v>47</v>
-      </c>
+      <c r="E65" s="235"/>
       <c r="F65" s="232"/>
       <c r="G65" s="231"/>
       <c r="H65" s="242"/>
@@ -35632,9 +34990,7 @@
       </c>
       <c r="C66" s="234"/>
       <c r="D66" s="234"/>
-      <c r="E66" s="235">
-        <v>48</v>
-      </c>
+      <c r="E66" s="235"/>
       <c r="F66" s="232"/>
       <c r="G66" s="231"/>
       <c r="H66" s="242"/>
@@ -35648,9 +35004,7 @@
       </c>
       <c r="C67" s="234"/>
       <c r="D67" s="234"/>
-      <c r="E67" s="235">
-        <v>49</v>
-      </c>
+      <c r="E67" s="235"/>
       <c r="F67" s="232"/>
       <c r="G67" s="231"/>
       <c r="H67" s="242"/>
@@ -35664,9 +35018,7 @@
       </c>
       <c r="C68" s="234"/>
       <c r="D68" s="234"/>
-      <c r="E68" s="235">
-        <v>50</v>
-      </c>
+      <c r="E68" s="235"/>
       <c r="F68" s="232"/>
       <c r="G68" s="231"/>
       <c r="H68" s="242"/>
@@ -35680,9 +35032,7 @@
       </c>
       <c r="C69" s="234"/>
       <c r="D69" s="234"/>
-      <c r="E69" s="235">
-        <v>51</v>
-      </c>
+      <c r="E69" s="235"/>
       <c r="F69" s="232"/>
       <c r="G69" s="231"/>
       <c r="H69" s="242"/>
@@ -35696,9 +35046,7 @@
       </c>
       <c r="C70" s="234"/>
       <c r="D70" s="234"/>
-      <c r="E70" s="235">
-        <v>52</v>
-      </c>
+      <c r="E70" s="235"/>
       <c r="F70" s="232"/>
       <c r="G70" s="231"/>
       <c r="H70" s="242"/>
@@ -35712,9 +35060,7 @@
       </c>
       <c r="C71" s="234"/>
       <c r="D71" s="234"/>
-      <c r="E71" s="235">
-        <v>53</v>
-      </c>
+      <c r="E71" s="235"/>
       <c r="F71" s="232"/>
       <c r="G71" s="231"/>
       <c r="H71" s="242"/>
@@ -35728,9 +35074,7 @@
       </c>
       <c r="C72" s="234"/>
       <c r="D72" s="234"/>
-      <c r="E72" s="235">
-        <v>54</v>
-      </c>
+      <c r="E72" s="235"/>
       <c r="F72" s="232"/>
       <c r="G72" s="231"/>
       <c r="H72" s="242"/>
@@ -35744,37 +35088,31 @@
       </c>
       <c r="C73" s="234"/>
       <c r="D73" s="234"/>
-      <c r="E73" s="235">
-        <v>55</v>
-      </c>
+      <c r="E73" s="235"/>
       <c r="F73" s="232"/>
       <c r="G73" s="231"/>
       <c r="H73" s="242"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="304" t="s">
+      <c r="A74" s="305" t="s">
         <v>1598</v>
       </c>
-      <c r="B74" s="312" t="s">
+      <c r="B74" s="313" t="s">
         <v>1599</v>
       </c>
       <c r="C74" s="234"/>
       <c r="D74" s="234"/>
-      <c r="E74" s="235">
-        <v>56</v>
-      </c>
+      <c r="E74" s="235"/>
       <c r="F74" s="232"/>
       <c r="G74" s="231"/>
       <c r="H74" s="242"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="271"/>
-      <c r="B75" s="313"/>
+      <c r="A75" s="272"/>
+      <c r="B75" s="314"/>
       <c r="C75" s="234"/>
       <c r="D75" s="234"/>
-      <c r="E75" s="235">
-        <v>57</v>
-      </c>
+      <c r="E75" s="235"/>
       <c r="F75" s="232"/>
       <c r="G75" s="231"/>
       <c r="H75" s="242"/>
@@ -35788,9 +35126,7 @@
       </c>
       <c r="C76" s="234"/>
       <c r="D76" s="234"/>
-      <c r="E76" s="235">
-        <v>58</v>
-      </c>
+      <c r="E76" s="235"/>
       <c r="F76" s="232"/>
       <c r="G76" s="231"/>
       <c r="H76" s="242"/>
@@ -35802,9 +35138,7 @@
       </c>
       <c r="C77" s="234"/>
       <c r="D77" s="234"/>
-      <c r="E77" s="235">
-        <v>59</v>
-      </c>
+      <c r="E77" s="235"/>
       <c r="F77" s="232"/>
       <c r="G77" s="231"/>
       <c r="H77" s="242"/>
@@ -35818,9 +35152,7 @@
       </c>
       <c r="C78" s="234"/>
       <c r="D78" s="234"/>
-      <c r="E78" s="235">
-        <v>60</v>
-      </c>
+      <c r="E78" s="235"/>
       <c r="F78" s="232"/>
       <c r="G78" s="231"/>
       <c r="H78" s="242"/>
@@ -35832,9 +35164,7 @@
       </c>
       <c r="C79" s="234"/>
       <c r="D79" s="234"/>
-      <c r="E79" s="235">
-        <v>61</v>
-      </c>
+      <c r="E79" s="235"/>
       <c r="F79" s="232"/>
       <c r="G79" s="231"/>
       <c r="H79" s="242"/>
@@ -35846,9 +35176,7 @@
       </c>
       <c r="C80" s="234"/>
       <c r="D80" s="234"/>
-      <c r="E80" s="235">
-        <v>62</v>
-      </c>
+      <c r="E80" s="235"/>
       <c r="F80" s="232"/>
       <c r="G80" s="231"/>
       <c r="H80" s="242"/>
@@ -36070,7 +35398,7 @@
       <c r="A13" s="261" t="s">
         <v>1673</v>
       </c>
-      <c r="B13" s="315">
+      <c r="B13" s="270">
         <v>1234567890.12345</v>
       </c>
       <c r="H13" s="241" t="s">
